--- a/Cash Flow English.xlsx
+++ b/Cash Flow English.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0852c0c11891ff46/Work/Code/Accounting/Cash-Flow/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{847037F4-B34B-4955-8471-B307393648A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5310E4D-06DE-4688-9A7E-78AA7B54E6F4}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{847037F4-B34B-4955-8471-B307393648A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2754428-0E6B-4815-B0C4-C546C790BC92}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15600" tabRatio="601" xr2:uid="{79B85D9D-132E-4007-BD0A-B81E1FE6E187}"/>
   </bookViews>
@@ -437,12 +437,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="0"/>
-      <name val="JetBrains Mono"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color theme="8"/>
       <name val="JetBrains Mono"/>
       <family val="3"/>
@@ -471,6 +465,12 @@
       <b/>
       <sz val="16"/>
       <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0" tint="-0.499984740745262"/>
       <name val="JetBrains Mono"/>
       <family val="3"/>
     </font>
@@ -604,92 +604,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -705,23 +633,92 @@
     <xf numFmtId="165" fontId="9" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -739,33 +736,6 @@
         <family val="3"/>
         <scheme val="none"/>
       </font>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="JetBrains Mono"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="JetBrains Mono"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <protection locked="1" hidden="0"/>
     </dxf>
@@ -2036,6 +2006,33 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="164" formatCode="* 0,###\ &quot;kg&quot;;\ 0\ &quot;kg&quot;;"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="JetBrains Mono"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="JetBrains Mono"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="1" hidden="0"/>
     </dxf>
     <dxf>
@@ -2445,10 +2442,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:lumMod val="40000"/>
-                <a:lumOff val="60000"/>
-              </a:schemeClr>
+              <a:schemeClr val="accent6"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2728,271 +2722,6 @@
           <c:val>
             <c:numRef>
               <c:f>Data!$E$5:$CM$5</c:f>
-              <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"??_-;_-@_-</c:formatCode>
-                <c:ptCount val="87"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -3017,9 +2746,8 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent3">
-                <a:lumMod val="40000"/>
-                <a:lumOff val="60000"/>
+              <a:schemeClr val="accent6">
+                <a:tint val="65000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
@@ -3300,271 +3028,6 @@
           <c:val>
             <c:numRef>
               <c:f>Data!$E$6:$CM$6</c:f>
-              <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"??_-;_-@_-</c:formatCode>
-                <c:ptCount val="87"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -3606,12 +3069,10 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
+                <a:schemeClr val="accent6">
+                  <a:shade val="65000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:prstDash val="dash"/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -3891,271 +3352,6 @@
           <c:val>
             <c:numRef>
               <c:f>Data!$E$7:$CM$7</c:f>
-              <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"??_-;_-@_-</c:formatCode>
-                <c:ptCount val="87"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -4996,104 +4192,104 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{827E0F88-9DCE-4C80-A4BB-3AE9264C224D}" name="Table1" displayName="Table1" ref="A8:CM10" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{827E0F88-9DCE-4C80-A4BB-3AE9264C224D}" name="Table1" displayName="Table1" ref="A8:CM10" totalsRowShown="0" headerRowDxfId="92" dataDxfId="91">
   <autoFilter ref="A8:CM10" xr:uid="{827E0F88-9DCE-4C80-A4BB-3AE9264C224D}"/>
   <tableColumns count="91">
-    <tableColumn id="1" xr3:uid="{228B23E8-D0E2-4B12-B212-33026DC36A89}" name="Type" dataDxfId="92"/>
-    <tableColumn id="57" xr3:uid="{B8CD05FD-BB19-44F3-A54D-1BFA15C4DA29}" name="isFilter" dataDxfId="91">
+    <tableColumn id="1" xr3:uid="{228B23E8-D0E2-4B12-B212-33026DC36A89}" name="Type" dataDxfId="90"/>
+    <tableColumn id="57" xr3:uid="{B8CD05FD-BB19-44F3-A54D-1BFA15C4DA29}" name="isFilter" dataDxfId="89">
       <calculatedColumnFormula>SUBTOTAL(103, Table1[[#This Row],[Type]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="56" xr3:uid="{6D595FFB-DCF4-4A49-A6B5-A055B482B89C}" name="Title" dataDxfId="90"/>
-    <tableColumn id="2" xr3:uid="{5ABC0F44-4D5D-41C5-9B01-28F26662FE8B}" name="Sum" dataDxfId="89">
+    <tableColumn id="56" xr3:uid="{6D595FFB-DCF4-4A49-A6B5-A055B482B89C}" name="Title" dataDxfId="88"/>
+    <tableColumn id="2" xr3:uid="{5ABC0F44-4D5D-41C5-9B01-28F26662FE8B}" name="Sum" dataDxfId="87">
       <calculatedColumnFormula>SUM(Table1[[#This Row],[w1]:[w53]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{BC09EF84-85FF-4E4E-B736-E3D5250A483F}" name="w1" dataDxfId="88"/>
-    <tableColumn id="4" xr3:uid="{29513D0A-DB46-400F-8487-EDD6922D4304}" name="w2" dataDxfId="87"/>
-    <tableColumn id="5" xr3:uid="{7E3170D5-3786-4B37-8E76-1755000941D6}" name="w3" dataDxfId="86"/>
-    <tableColumn id="6" xr3:uid="{EDC30643-63F8-4CF1-82C6-3C9E34AA3CB2}" name="w4" dataDxfId="85"/>
-    <tableColumn id="7" xr3:uid="{5749E184-3232-40F2-A985-AAE648242714}" name="w5" dataDxfId="84"/>
-    <tableColumn id="8" xr3:uid="{C3077793-AFE3-402A-B880-725A764BF824}" name="w6" dataDxfId="83"/>
-    <tableColumn id="9" xr3:uid="{EE501971-3DBC-4B5B-9FF9-0405E2AA2AF0}" name="w7" dataDxfId="82"/>
-    <tableColumn id="10" xr3:uid="{40276A41-2DC8-42B3-B037-4C4BDA0A5C9D}" name="w8" dataDxfId="81"/>
-    <tableColumn id="11" xr3:uid="{0E46F9F1-2CF9-4E94-909A-17F6344F1210}" name="w9" dataDxfId="80"/>
-    <tableColumn id="12" xr3:uid="{3C15558B-2662-41E3-B254-A67211D0F74E}" name="w10" dataDxfId="79"/>
-    <tableColumn id="13" xr3:uid="{8C4EB03D-896A-4F02-B3FD-EE6B1D690364}" name="w11" dataDxfId="78"/>
-    <tableColumn id="14" xr3:uid="{B91AF945-39E5-42D8-9799-845A31E1BF6F}" name="w12" dataDxfId="77"/>
-    <tableColumn id="15" xr3:uid="{606DEDD0-6F62-46B1-8B0C-2D6BB7CE1F62}" name="w13" dataDxfId="76"/>
-    <tableColumn id="16" xr3:uid="{CC80E201-A501-49CD-859F-A5BFCDE98CC6}" name="w14" dataDxfId="75"/>
-    <tableColumn id="17" xr3:uid="{CEBE3381-9C85-4108-BCBE-E6EA9AA3F242}" name="w15" dataDxfId="74"/>
-    <tableColumn id="18" xr3:uid="{074F6A6D-C0D3-4F5F-8307-93305642DD03}" name="w16" dataDxfId="73"/>
-    <tableColumn id="19" xr3:uid="{3526B270-FBE3-4E33-98CD-373C66595442}" name="w17" dataDxfId="72"/>
-    <tableColumn id="20" xr3:uid="{2EF7F974-AB3B-4A8A-95E9-F92E5635E904}" name="w18" dataDxfId="71"/>
-    <tableColumn id="21" xr3:uid="{1D7A14E1-D3A0-458A-BFA1-10A530DDEC7F}" name="w19" dataDxfId="70"/>
-    <tableColumn id="22" xr3:uid="{26FB226C-2DA1-47AB-8A8E-2304F590E094}" name="w20" dataDxfId="69"/>
-    <tableColumn id="23" xr3:uid="{AFF29E2A-BC6B-43DC-B3C5-3B09B0882E53}" name="w21" dataDxfId="68"/>
-    <tableColumn id="24" xr3:uid="{E6F980E9-76D7-4833-BD98-7D0B471C8FA7}" name="w22" dataDxfId="67"/>
-    <tableColumn id="25" xr3:uid="{5346D994-571A-4B93-B5A9-4AB09E8BBF44}" name="w23" dataDxfId="66"/>
-    <tableColumn id="26" xr3:uid="{42404044-8772-458E-8632-77FBC4F08664}" name="w24" dataDxfId="65"/>
-    <tableColumn id="27" xr3:uid="{E571A43A-BCB9-403D-8B84-C152B2318523}" name="w25" dataDxfId="64"/>
-    <tableColumn id="28" xr3:uid="{B48391D2-42A7-4760-85BD-4E1095A3C95A}" name="w26" dataDxfId="63"/>
-    <tableColumn id="29" xr3:uid="{D2B616DF-A7E9-4C08-B9DE-703C457EF917}" name="w27" dataDxfId="62"/>
-    <tableColumn id="30" xr3:uid="{CB202AAE-160D-4D90-ABB9-ADBD4D440D1F}" name="w28" dataDxfId="61"/>
-    <tableColumn id="31" xr3:uid="{96F22171-C2DD-4742-8BC3-A778739C7EE0}" name="w29" dataDxfId="60"/>
-    <tableColumn id="32" xr3:uid="{919B2BDF-DBDC-4041-9B67-8C5E3DED584D}" name="w30" dataDxfId="59"/>
-    <tableColumn id="33" xr3:uid="{4E05B930-023D-4623-A32F-0814890D5FFD}" name="w31" dataDxfId="58"/>
-    <tableColumn id="34" xr3:uid="{459BA982-A901-42F0-ACF2-A431F2718D80}" name="w32" dataDxfId="57"/>
-    <tableColumn id="35" xr3:uid="{1574A07E-277D-4FCB-B18B-B6E96F7F48B3}" name="w33" dataDxfId="56"/>
-    <tableColumn id="36" xr3:uid="{384512D4-50C9-4353-8C50-F3D6DF7C95FC}" name="w34" dataDxfId="55"/>
-    <tableColumn id="37" xr3:uid="{299EF4B6-09BE-4CF9-A254-852AF79252E4}" name="w35" dataDxfId="54"/>
-    <tableColumn id="38" xr3:uid="{61A1B048-2305-4992-A179-C1F5368E2D43}" name="w36" dataDxfId="53"/>
-    <tableColumn id="39" xr3:uid="{9AF02C86-3704-4C53-8DE3-DC7E7257BAEB}" name="w37" dataDxfId="52"/>
-    <tableColumn id="40" xr3:uid="{8AB4B8AD-2566-4293-9A79-816A11AE5D2F}" name="w38" dataDxfId="51"/>
-    <tableColumn id="41" xr3:uid="{B803BAC9-6EB7-4BBC-BB79-228DD1478EF1}" name="w39" dataDxfId="50"/>
-    <tableColumn id="42" xr3:uid="{A460385C-C837-47BE-88CF-115817BD0E5C}" name="w40" dataDxfId="49"/>
-    <tableColumn id="43" xr3:uid="{57BAFA50-0811-427A-9A12-CEEF61CFA40B}" name="w41" dataDxfId="48"/>
-    <tableColumn id="44" xr3:uid="{D6021E58-B816-45E5-B4DF-0FD5D5DCFBBF}" name="w42" dataDxfId="47"/>
-    <tableColumn id="45" xr3:uid="{3A8E0C5D-FF14-47DC-93C4-5F240C5312D3}" name="w43" dataDxfId="46"/>
-    <tableColumn id="46" xr3:uid="{DA38BA2F-0576-4A24-9FD9-A39E4709F612}" name="w44" dataDxfId="45"/>
-    <tableColumn id="47" xr3:uid="{0DBD556C-14A9-473D-8F2C-90D56ECF5B87}" name="w45" dataDxfId="44"/>
-    <tableColumn id="48" xr3:uid="{A25D0319-06E1-4C59-9EE7-062F89DC2250}" name="w46" dataDxfId="43"/>
-    <tableColumn id="49" xr3:uid="{B44FB6B3-D1FB-4973-BA6C-3363130E9C9C}" name="w47" dataDxfId="42"/>
-    <tableColumn id="50" xr3:uid="{106A8EC1-FE90-4B1E-8395-C23DEB2AE968}" name="w48" dataDxfId="41"/>
-    <tableColumn id="51" xr3:uid="{9AEFE9C5-B843-4D25-8669-183FB4798C9C}" name="w49" dataDxfId="40"/>
-    <tableColumn id="52" xr3:uid="{747870F5-B194-43FE-8479-7CE1E97F4EE9}" name="w50" dataDxfId="39"/>
-    <tableColumn id="53" xr3:uid="{EBE0589D-4CF4-4159-B55B-8B0B70682BD9}" name="w51" dataDxfId="38"/>
-    <tableColumn id="54" xr3:uid="{F3E793CD-08A8-4E76-AB32-1A5CAA0B7294}" name="w52" dataDxfId="37"/>
-    <tableColumn id="55" xr3:uid="{5643F41D-750B-4361-BB69-1C067C81115A}" name="w53" dataDxfId="36"/>
-    <tableColumn id="58" xr3:uid="{87B041C6-3276-483E-9C3E-69B556532B84}" name="w54" dataDxfId="35"/>
-    <tableColumn id="59" xr3:uid="{186B4A9B-A168-428A-8287-F458F39CB0E3}" name="w55" dataDxfId="34"/>
-    <tableColumn id="60" xr3:uid="{48EEB35A-C9E6-42AF-A9BC-C93F29FDA8AE}" name="w56" dataDxfId="33"/>
-    <tableColumn id="61" xr3:uid="{3C16935A-636E-4178-9CAA-675478E07658}" name="w57" dataDxfId="32"/>
-    <tableColumn id="62" xr3:uid="{138D6815-02FA-400C-B299-A3BDBFF941F8}" name="w58" dataDxfId="31"/>
-    <tableColumn id="63" xr3:uid="{AA9B3F10-7E39-4410-8B82-102C6792489D}" name="w59" dataDxfId="30"/>
-    <tableColumn id="64" xr3:uid="{79756940-2E82-407D-BB77-B4AE68F11675}" name="w60" dataDxfId="29"/>
-    <tableColumn id="65" xr3:uid="{0EC98C5A-CF5E-4C59-AB72-79613B65DD68}" name="w61" dataDxfId="28"/>
-    <tableColumn id="66" xr3:uid="{34343F8D-1241-4E30-B2F4-E415F8E06ADF}" name="w62" dataDxfId="27"/>
-    <tableColumn id="67" xr3:uid="{42DAB5B5-FDC1-4540-B3C4-DFFDE8351DFB}" name="w63" dataDxfId="26"/>
-    <tableColumn id="68" xr3:uid="{564750F8-F827-470F-85F8-546ED04D9397}" name="w64" dataDxfId="25"/>
-    <tableColumn id="69" xr3:uid="{61C3FEB5-E146-47DE-9B1D-7CA0AD577454}" name="w65" dataDxfId="24"/>
-    <tableColumn id="70" xr3:uid="{393447F8-C177-43F6-95EC-B40FC9A41C17}" name="w66" dataDxfId="23"/>
-    <tableColumn id="71" xr3:uid="{C26227F2-2656-4B0C-8C7B-AAE5553E5987}" name="w67" dataDxfId="22"/>
-    <tableColumn id="72" xr3:uid="{9D02F9A0-FF18-4E0C-9C85-A7CD4B8A02E9}" name="w68" dataDxfId="21"/>
-    <tableColumn id="73" xr3:uid="{D7F29341-C2D4-4ADE-A7A3-83082F9C38F6}" name="w69" dataDxfId="20"/>
-    <tableColumn id="74" xr3:uid="{B79463CA-1487-4171-84D5-4A47A253D01D}" name="w70" dataDxfId="19"/>
-    <tableColumn id="75" xr3:uid="{3A541828-21FF-46EA-91BD-6C360D48BAAD}" name="w71" dataDxfId="18"/>
-    <tableColumn id="76" xr3:uid="{12D1D5B3-6A8E-46FA-8EA3-A256A105E307}" name="w72" dataDxfId="17"/>
-    <tableColumn id="77" xr3:uid="{ECD24C8A-FD0B-4F56-8F02-542B24FB62FE}" name="w73" dataDxfId="16"/>
-    <tableColumn id="78" xr3:uid="{5D2FD2B7-24CD-4060-8577-6730D6C99B30}" name="w74" dataDxfId="15"/>
-    <tableColumn id="79" xr3:uid="{42D0255D-79B7-46E7-813E-A95839C1E9D2}" name="w75" dataDxfId="14"/>
-    <tableColumn id="80" xr3:uid="{43CAB660-97F4-4F36-99D4-5DD723EC8EA9}" name="w76" dataDxfId="13"/>
-    <tableColumn id="81" xr3:uid="{5841A504-191F-4D5E-A675-B96BCEC0D6B7}" name="w77" dataDxfId="12"/>
-    <tableColumn id="82" xr3:uid="{76B44F75-AFB9-4556-A3BC-5B9C6D2BA0FC}" name="w78" dataDxfId="11"/>
-    <tableColumn id="83" xr3:uid="{65D8AF63-927E-41F8-BC15-CBFF3A4C7E79}" name="w79" dataDxfId="10"/>
-    <tableColumn id="84" xr3:uid="{ED288058-327B-4544-83E2-E48B9E052294}" name="w80" dataDxfId="9"/>
-    <tableColumn id="85" xr3:uid="{81C214B6-29F8-425D-9C13-12787625B9FF}" name="w81" dataDxfId="8"/>
-    <tableColumn id="86" xr3:uid="{0763049B-4B76-44F8-8714-B556E59662DE}" name="w82" dataDxfId="7"/>
-    <tableColumn id="87" xr3:uid="{04F3E466-14F0-41EB-9250-47E0DF13F73D}" name="w83" dataDxfId="6"/>
-    <tableColumn id="88" xr3:uid="{8DA09647-81CB-4CE1-8AA4-21934B231C83}" name="w84" dataDxfId="5"/>
-    <tableColumn id="89" xr3:uid="{F78E8AA8-BF1C-457D-83F1-D3945D356DEE}" name="w85" dataDxfId="4"/>
-    <tableColumn id="90" xr3:uid="{1D80D9DC-F674-47B0-BC4E-4087F07D6136}" name="w86" dataDxfId="3"/>
-    <tableColumn id="91" xr3:uid="{1A0F1507-50BB-4204-A983-6FB9B2243250}" name="w87" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{BC09EF84-85FF-4E4E-B736-E3D5250A483F}" name="w1" dataDxfId="86"/>
+    <tableColumn id="4" xr3:uid="{29513D0A-DB46-400F-8487-EDD6922D4304}" name="w2" dataDxfId="85"/>
+    <tableColumn id="5" xr3:uid="{7E3170D5-3786-4B37-8E76-1755000941D6}" name="w3" dataDxfId="84"/>
+    <tableColumn id="6" xr3:uid="{EDC30643-63F8-4CF1-82C6-3C9E34AA3CB2}" name="w4" dataDxfId="83"/>
+    <tableColumn id="7" xr3:uid="{5749E184-3232-40F2-A985-AAE648242714}" name="w5" dataDxfId="82"/>
+    <tableColumn id="8" xr3:uid="{C3077793-AFE3-402A-B880-725A764BF824}" name="w6" dataDxfId="81"/>
+    <tableColumn id="9" xr3:uid="{EE501971-3DBC-4B5B-9FF9-0405E2AA2AF0}" name="w7" dataDxfId="80"/>
+    <tableColumn id="10" xr3:uid="{40276A41-2DC8-42B3-B037-4C4BDA0A5C9D}" name="w8" dataDxfId="79"/>
+    <tableColumn id="11" xr3:uid="{0E46F9F1-2CF9-4E94-909A-17F6344F1210}" name="w9" dataDxfId="78"/>
+    <tableColumn id="12" xr3:uid="{3C15558B-2662-41E3-B254-A67211D0F74E}" name="w10" dataDxfId="77"/>
+    <tableColumn id="13" xr3:uid="{8C4EB03D-896A-4F02-B3FD-EE6B1D690364}" name="w11" dataDxfId="76"/>
+    <tableColumn id="14" xr3:uid="{B91AF945-39E5-42D8-9799-845A31E1BF6F}" name="w12" dataDxfId="75"/>
+    <tableColumn id="15" xr3:uid="{606DEDD0-6F62-46B1-8B0C-2D6BB7CE1F62}" name="w13" dataDxfId="74"/>
+    <tableColumn id="16" xr3:uid="{CC80E201-A501-49CD-859F-A5BFCDE98CC6}" name="w14" dataDxfId="73"/>
+    <tableColumn id="17" xr3:uid="{CEBE3381-9C85-4108-BCBE-E6EA9AA3F242}" name="w15" dataDxfId="72"/>
+    <tableColumn id="18" xr3:uid="{074F6A6D-C0D3-4F5F-8307-93305642DD03}" name="w16" dataDxfId="71"/>
+    <tableColumn id="19" xr3:uid="{3526B270-FBE3-4E33-98CD-373C66595442}" name="w17" dataDxfId="70"/>
+    <tableColumn id="20" xr3:uid="{2EF7F974-AB3B-4A8A-95E9-F92E5635E904}" name="w18" dataDxfId="69"/>
+    <tableColumn id="21" xr3:uid="{1D7A14E1-D3A0-458A-BFA1-10A530DDEC7F}" name="w19" dataDxfId="68"/>
+    <tableColumn id="22" xr3:uid="{26FB226C-2DA1-47AB-8A8E-2304F590E094}" name="w20" dataDxfId="67"/>
+    <tableColumn id="23" xr3:uid="{AFF29E2A-BC6B-43DC-B3C5-3B09B0882E53}" name="w21" dataDxfId="66"/>
+    <tableColumn id="24" xr3:uid="{E6F980E9-76D7-4833-BD98-7D0B471C8FA7}" name="w22" dataDxfId="65"/>
+    <tableColumn id="25" xr3:uid="{5346D994-571A-4B93-B5A9-4AB09E8BBF44}" name="w23" dataDxfId="64"/>
+    <tableColumn id="26" xr3:uid="{42404044-8772-458E-8632-77FBC4F08664}" name="w24" dataDxfId="63"/>
+    <tableColumn id="27" xr3:uid="{E571A43A-BCB9-403D-8B84-C152B2318523}" name="w25" dataDxfId="62"/>
+    <tableColumn id="28" xr3:uid="{B48391D2-42A7-4760-85BD-4E1095A3C95A}" name="w26" dataDxfId="61"/>
+    <tableColumn id="29" xr3:uid="{D2B616DF-A7E9-4C08-B9DE-703C457EF917}" name="w27" dataDxfId="60"/>
+    <tableColumn id="30" xr3:uid="{CB202AAE-160D-4D90-ABB9-ADBD4D440D1F}" name="w28" dataDxfId="59"/>
+    <tableColumn id="31" xr3:uid="{96F22171-C2DD-4742-8BC3-A778739C7EE0}" name="w29" dataDxfId="58"/>
+    <tableColumn id="32" xr3:uid="{919B2BDF-DBDC-4041-9B67-8C5E3DED584D}" name="w30" dataDxfId="57"/>
+    <tableColumn id="33" xr3:uid="{4E05B930-023D-4623-A32F-0814890D5FFD}" name="w31" dataDxfId="56"/>
+    <tableColumn id="34" xr3:uid="{459BA982-A901-42F0-ACF2-A431F2718D80}" name="w32" dataDxfId="55"/>
+    <tableColumn id="35" xr3:uid="{1574A07E-277D-4FCB-B18B-B6E96F7F48B3}" name="w33" dataDxfId="54"/>
+    <tableColumn id="36" xr3:uid="{384512D4-50C9-4353-8C50-F3D6DF7C95FC}" name="w34" dataDxfId="53"/>
+    <tableColumn id="37" xr3:uid="{299EF4B6-09BE-4CF9-A254-852AF79252E4}" name="w35" dataDxfId="52"/>
+    <tableColumn id="38" xr3:uid="{61A1B048-2305-4992-A179-C1F5368E2D43}" name="w36" dataDxfId="51"/>
+    <tableColumn id="39" xr3:uid="{9AF02C86-3704-4C53-8DE3-DC7E7257BAEB}" name="w37" dataDxfId="50"/>
+    <tableColumn id="40" xr3:uid="{8AB4B8AD-2566-4293-9A79-816A11AE5D2F}" name="w38" dataDxfId="49"/>
+    <tableColumn id="41" xr3:uid="{B803BAC9-6EB7-4BBC-BB79-228DD1478EF1}" name="w39" dataDxfId="48"/>
+    <tableColumn id="42" xr3:uid="{A460385C-C837-47BE-88CF-115817BD0E5C}" name="w40" dataDxfId="47"/>
+    <tableColumn id="43" xr3:uid="{57BAFA50-0811-427A-9A12-CEEF61CFA40B}" name="w41" dataDxfId="46"/>
+    <tableColumn id="44" xr3:uid="{D6021E58-B816-45E5-B4DF-0FD5D5DCFBBF}" name="w42" dataDxfId="45"/>
+    <tableColumn id="45" xr3:uid="{3A8E0C5D-FF14-47DC-93C4-5F240C5312D3}" name="w43" dataDxfId="44"/>
+    <tableColumn id="46" xr3:uid="{DA38BA2F-0576-4A24-9FD9-A39E4709F612}" name="w44" dataDxfId="43"/>
+    <tableColumn id="47" xr3:uid="{0DBD556C-14A9-473D-8F2C-90D56ECF5B87}" name="w45" dataDxfId="42"/>
+    <tableColumn id="48" xr3:uid="{A25D0319-06E1-4C59-9EE7-062F89DC2250}" name="w46" dataDxfId="41"/>
+    <tableColumn id="49" xr3:uid="{B44FB6B3-D1FB-4973-BA6C-3363130E9C9C}" name="w47" dataDxfId="40"/>
+    <tableColumn id="50" xr3:uid="{106A8EC1-FE90-4B1E-8395-C23DEB2AE968}" name="w48" dataDxfId="39"/>
+    <tableColumn id="51" xr3:uid="{9AEFE9C5-B843-4D25-8669-183FB4798C9C}" name="w49" dataDxfId="38"/>
+    <tableColumn id="52" xr3:uid="{747870F5-B194-43FE-8479-7CE1E97F4EE9}" name="w50" dataDxfId="37"/>
+    <tableColumn id="53" xr3:uid="{EBE0589D-4CF4-4159-B55B-8B0B70682BD9}" name="w51" dataDxfId="36"/>
+    <tableColumn id="54" xr3:uid="{F3E793CD-08A8-4E76-AB32-1A5CAA0B7294}" name="w52" dataDxfId="35"/>
+    <tableColumn id="55" xr3:uid="{5643F41D-750B-4361-BB69-1C067C81115A}" name="w53" dataDxfId="34"/>
+    <tableColumn id="58" xr3:uid="{87B041C6-3276-483E-9C3E-69B556532B84}" name="w54" dataDxfId="33"/>
+    <tableColumn id="59" xr3:uid="{186B4A9B-A168-428A-8287-F458F39CB0E3}" name="w55" dataDxfId="32"/>
+    <tableColumn id="60" xr3:uid="{48EEB35A-C9E6-42AF-A9BC-C93F29FDA8AE}" name="w56" dataDxfId="31"/>
+    <tableColumn id="61" xr3:uid="{3C16935A-636E-4178-9CAA-675478E07658}" name="w57" dataDxfId="30"/>
+    <tableColumn id="62" xr3:uid="{138D6815-02FA-400C-B299-A3BDBFF941F8}" name="w58" dataDxfId="29"/>
+    <tableColumn id="63" xr3:uid="{AA9B3F10-7E39-4410-8B82-102C6792489D}" name="w59" dataDxfId="28"/>
+    <tableColumn id="64" xr3:uid="{79756940-2E82-407D-BB77-B4AE68F11675}" name="w60" dataDxfId="27"/>
+    <tableColumn id="65" xr3:uid="{0EC98C5A-CF5E-4C59-AB72-79613B65DD68}" name="w61" dataDxfId="26"/>
+    <tableColumn id="66" xr3:uid="{34343F8D-1241-4E30-B2F4-E415F8E06ADF}" name="w62" dataDxfId="25"/>
+    <tableColumn id="67" xr3:uid="{42DAB5B5-FDC1-4540-B3C4-DFFDE8351DFB}" name="w63" dataDxfId="24"/>
+    <tableColumn id="68" xr3:uid="{564750F8-F827-470F-85F8-546ED04D9397}" name="w64" dataDxfId="23"/>
+    <tableColumn id="69" xr3:uid="{61C3FEB5-E146-47DE-9B1D-7CA0AD577454}" name="w65" dataDxfId="22"/>
+    <tableColumn id="70" xr3:uid="{393447F8-C177-43F6-95EC-B40FC9A41C17}" name="w66" dataDxfId="21"/>
+    <tableColumn id="71" xr3:uid="{C26227F2-2656-4B0C-8C7B-AAE5553E5987}" name="w67" dataDxfId="20"/>
+    <tableColumn id="72" xr3:uid="{9D02F9A0-FF18-4E0C-9C85-A7CD4B8A02E9}" name="w68" dataDxfId="19"/>
+    <tableColumn id="73" xr3:uid="{D7F29341-C2D4-4ADE-A7A3-83082F9C38F6}" name="w69" dataDxfId="18"/>
+    <tableColumn id="74" xr3:uid="{B79463CA-1487-4171-84D5-4A47A253D01D}" name="w70" dataDxfId="17"/>
+    <tableColumn id="75" xr3:uid="{3A541828-21FF-46EA-91BD-6C360D48BAAD}" name="w71" dataDxfId="16"/>
+    <tableColumn id="76" xr3:uid="{12D1D5B3-6A8E-46FA-8EA3-A256A105E307}" name="w72" dataDxfId="15"/>
+    <tableColumn id="77" xr3:uid="{ECD24C8A-FD0B-4F56-8F02-542B24FB62FE}" name="w73" dataDxfId="14"/>
+    <tableColumn id="78" xr3:uid="{5D2FD2B7-24CD-4060-8577-6730D6C99B30}" name="w74" dataDxfId="13"/>
+    <tableColumn id="79" xr3:uid="{42D0255D-79B7-46E7-813E-A95839C1E9D2}" name="w75" dataDxfId="12"/>
+    <tableColumn id="80" xr3:uid="{43CAB660-97F4-4F36-99D4-5DD723EC8EA9}" name="w76" dataDxfId="11"/>
+    <tableColumn id="81" xr3:uid="{5841A504-191F-4D5E-A675-B96BCEC0D6B7}" name="w77" dataDxfId="10"/>
+    <tableColumn id="82" xr3:uid="{76B44F75-AFB9-4556-A3BC-5B9C6D2BA0FC}" name="w78" dataDxfId="9"/>
+    <tableColumn id="83" xr3:uid="{65D8AF63-927E-41F8-BC15-CBFF3A4C7E79}" name="w79" dataDxfId="8"/>
+    <tableColumn id="84" xr3:uid="{ED288058-327B-4544-83E2-E48B9E052294}" name="w80" dataDxfId="7"/>
+    <tableColumn id="85" xr3:uid="{81C214B6-29F8-425D-9C13-12787625B9FF}" name="w81" dataDxfId="6"/>
+    <tableColumn id="86" xr3:uid="{0763049B-4B76-44F8-8714-B556E59662DE}" name="w82" dataDxfId="5"/>
+    <tableColumn id="87" xr3:uid="{04F3E466-14F0-41EB-9250-47E0DF13F73D}" name="w83" dataDxfId="4"/>
+    <tableColumn id="88" xr3:uid="{8DA09647-81CB-4CE1-8AA4-21934B231C83}" name="w84" dataDxfId="3"/>
+    <tableColumn id="89" xr3:uid="{F78E8AA8-BF1C-457D-83F1-D3945D356DEE}" name="w85" dataDxfId="2"/>
+    <tableColumn id="90" xr3:uid="{1D80D9DC-F674-47B0-BC4E-4087F07D6136}" name="w86" dataDxfId="1"/>
+    <tableColumn id="91" xr3:uid="{1A0F1507-50BB-4204-A983-6FB9B2243250}" name="w87" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5404,2333 +4600,2333 @@
   <dimension ref="A1:CM10"/>
   <sheetFormatPr defaultColWidth="9.625" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.875" style="44" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.625" style="44" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="18.375" style="44" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="45" customWidth="1"/>
-    <col min="5" max="5" width="7.625" style="44" customWidth="1"/>
-    <col min="6" max="8" width="7.625" style="44" customWidth="1" outlineLevel="2"/>
-    <col min="9" max="9" width="7.625" style="44" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="13" width="7.625" style="44" customWidth="1" outlineLevel="2"/>
-    <col min="14" max="14" width="7.625" style="44" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="17" width="7.625" style="44" customWidth="1" outlineLevel="2"/>
-    <col min="18" max="18" width="7.625" style="44" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="22" width="7.625" style="44" customWidth="1" outlineLevel="2"/>
-    <col min="23" max="23" width="7.625" style="44" customWidth="1"/>
-    <col min="24" max="26" width="7.625" style="44" customWidth="1" outlineLevel="2"/>
-    <col min="27" max="27" width="7.625" style="44" customWidth="1" outlineLevel="1"/>
-    <col min="28" max="30" width="7.625" style="44" customWidth="1" outlineLevel="2"/>
-    <col min="31" max="31" width="7.625" style="44" customWidth="1" outlineLevel="1"/>
-    <col min="32" max="35" width="7.625" style="44" customWidth="1" outlineLevel="2"/>
-    <col min="36" max="36" width="7.625" style="44" customWidth="1" outlineLevel="1"/>
-    <col min="37" max="39" width="7.625" style="44" customWidth="1" outlineLevel="2"/>
-    <col min="40" max="40" width="7.625" style="44" customWidth="1" outlineLevel="1"/>
-    <col min="41" max="43" width="7.625" style="44" customWidth="1" outlineLevel="2"/>
-    <col min="44" max="44" width="7.625" style="44" customWidth="1" outlineLevel="1"/>
-    <col min="45" max="48" width="7.625" style="44" customWidth="1" outlineLevel="2"/>
-    <col min="49" max="49" width="7.625" style="44" customWidth="1" outlineLevel="1"/>
-    <col min="50" max="52" width="7.625" style="44" customWidth="1" outlineLevel="2"/>
-    <col min="53" max="53" width="7.625" style="44" customWidth="1" outlineLevel="1"/>
-    <col min="54" max="57" width="7.625" style="44" customWidth="1" outlineLevel="2"/>
-    <col min="58" max="58" width="7.625" style="44" customWidth="1" outlineLevel="1"/>
-    <col min="59" max="61" width="7.625" style="44" customWidth="1" outlineLevel="2"/>
-    <col min="62" max="62" width="7.625" style="44" customWidth="1" outlineLevel="1"/>
-    <col min="63" max="65" width="7.625" style="44" customWidth="1" outlineLevel="2"/>
-    <col min="66" max="66" width="7.625" style="44" customWidth="1" outlineLevel="1"/>
-    <col min="67" max="70" width="7.625" style="44" customWidth="1" outlineLevel="2"/>
-    <col min="71" max="71" width="7.625" style="44" customWidth="1" outlineLevel="1"/>
-    <col min="72" max="74" width="7.625" style="44" customWidth="1" outlineLevel="2"/>
-    <col min="75" max="75" width="7.625" style="44" customWidth="1"/>
-    <col min="76" max="78" width="7.625" style="44" customWidth="1" outlineLevel="2"/>
-    <col min="79" max="79" width="7.625" style="44" customWidth="1" outlineLevel="1"/>
-    <col min="80" max="83" width="7.625" style="44" customWidth="1" outlineLevel="2"/>
-    <col min="84" max="84" width="7.625" style="44" customWidth="1" outlineLevel="1"/>
-    <col min="85" max="87" width="7.625" style="44" customWidth="1" outlineLevel="2"/>
-    <col min="88" max="88" width="7.625" style="44" customWidth="1" outlineLevel="1"/>
-    <col min="89" max="91" width="7.625" style="44" customWidth="1" outlineLevel="2"/>
-    <col min="92" max="16384" width="9.625" style="44"/>
+    <col min="1" max="1" width="7.875" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.625" style="18" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="18.375" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="19" customWidth="1"/>
+    <col min="5" max="5" width="7.625" style="18" customWidth="1"/>
+    <col min="6" max="8" width="7.625" style="18" customWidth="1" outlineLevel="2"/>
+    <col min="9" max="9" width="7.625" style="18" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="13" width="7.625" style="18" customWidth="1" outlineLevel="2"/>
+    <col min="14" max="14" width="7.625" style="18" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="17" width="7.625" style="18" customWidth="1" outlineLevel="2"/>
+    <col min="18" max="18" width="7.625" style="18" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="22" width="7.625" style="18" customWidth="1" outlineLevel="2"/>
+    <col min="23" max="23" width="7.625" style="18" customWidth="1"/>
+    <col min="24" max="26" width="7.625" style="18" customWidth="1" outlineLevel="2"/>
+    <col min="27" max="27" width="7.625" style="18" customWidth="1" outlineLevel="1"/>
+    <col min="28" max="30" width="7.625" style="18" customWidth="1" outlineLevel="2"/>
+    <col min="31" max="31" width="7.625" style="18" customWidth="1" outlineLevel="1"/>
+    <col min="32" max="35" width="7.625" style="18" customWidth="1" outlineLevel="2"/>
+    <col min="36" max="36" width="7.625" style="18" customWidth="1" outlineLevel="1"/>
+    <col min="37" max="39" width="7.625" style="18" customWidth="1" outlineLevel="2"/>
+    <col min="40" max="40" width="7.625" style="18" customWidth="1" outlineLevel="1"/>
+    <col min="41" max="43" width="7.625" style="18" customWidth="1" outlineLevel="2"/>
+    <col min="44" max="44" width="7.625" style="18" customWidth="1" outlineLevel="1"/>
+    <col min="45" max="48" width="7.625" style="18" customWidth="1" outlineLevel="2"/>
+    <col min="49" max="49" width="7.625" style="18" customWidth="1" outlineLevel="1"/>
+    <col min="50" max="52" width="7.625" style="18" customWidth="1" outlineLevel="2"/>
+    <col min="53" max="53" width="7.625" style="18" customWidth="1" outlineLevel="1"/>
+    <col min="54" max="57" width="7.625" style="18" customWidth="1" outlineLevel="2"/>
+    <col min="58" max="58" width="7.625" style="18" customWidth="1" outlineLevel="1"/>
+    <col min="59" max="61" width="7.625" style="18" customWidth="1" outlineLevel="2"/>
+    <col min="62" max="62" width="7.625" style="18" customWidth="1" outlineLevel="1"/>
+    <col min="63" max="65" width="7.625" style="18" customWidth="1" outlineLevel="2"/>
+    <col min="66" max="66" width="7.625" style="18" customWidth="1" outlineLevel="1"/>
+    <col min="67" max="70" width="7.625" style="18" customWidth="1" outlineLevel="2"/>
+    <col min="71" max="71" width="7.625" style="18" customWidth="1" outlineLevel="1"/>
+    <col min="72" max="74" width="7.625" style="18" customWidth="1" outlineLevel="2"/>
+    <col min="75" max="75" width="7.625" style="18" customWidth="1"/>
+    <col min="76" max="78" width="7.625" style="18" customWidth="1" outlineLevel="2"/>
+    <col min="79" max="79" width="7.625" style="18" customWidth="1" outlineLevel="1"/>
+    <col min="80" max="83" width="7.625" style="18" customWidth="1" outlineLevel="2"/>
+    <col min="84" max="84" width="7.625" style="18" customWidth="1" outlineLevel="1"/>
+    <col min="85" max="87" width="7.625" style="18" customWidth="1" outlineLevel="2"/>
+    <col min="88" max="88" width="7.625" style="18" customWidth="1" outlineLevel="1"/>
+    <col min="89" max="91" width="7.625" style="18" customWidth="1" outlineLevel="2"/>
+    <col min="92" max="16384" width="9.625" style="18"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:91" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.35">
       <c r="D1" s="2"/>
-      <c r="E1" s="46">
+      <c r="E1" s="20">
         <v>2026</v>
       </c>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="46"/>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="46"/>
-      <c r="S1" s="46"/>
-      <c r="T1" s="46"/>
-      <c r="U1" s="46"/>
-      <c r="V1" s="46"/>
-      <c r="W1" s="46">
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20">
         <v>2027</v>
       </c>
-      <c r="X1" s="46"/>
-      <c r="Y1" s="46"/>
-      <c r="Z1" s="46"/>
-      <c r="AA1" s="46"/>
-      <c r="AB1" s="46"/>
-      <c r="AC1" s="46"/>
-      <c r="AD1" s="46"/>
-      <c r="AE1" s="46"/>
-      <c r="AF1" s="46"/>
-      <c r="AG1" s="46"/>
-      <c r="AH1" s="46"/>
-      <c r="AI1" s="46"/>
-      <c r="AJ1" s="46"/>
-      <c r="AK1" s="46"/>
-      <c r="AL1" s="46"/>
-      <c r="AM1" s="46"/>
-      <c r="AN1" s="46"/>
-      <c r="AO1" s="46"/>
-      <c r="AP1" s="46"/>
-      <c r="AQ1" s="46"/>
-      <c r="AR1" s="46"/>
-      <c r="AS1" s="46"/>
-      <c r="AT1" s="46"/>
-      <c r="AU1" s="46"/>
-      <c r="AV1" s="46"/>
-      <c r="AW1" s="46"/>
-      <c r="AX1" s="46"/>
-      <c r="AY1" s="46"/>
-      <c r="AZ1" s="46"/>
-      <c r="BA1" s="46"/>
-      <c r="BB1" s="46"/>
-      <c r="BC1" s="46"/>
-      <c r="BD1" s="46"/>
-      <c r="BE1" s="46"/>
-      <c r="BF1" s="46"/>
-      <c r="BG1" s="46"/>
-      <c r="BH1" s="46"/>
-      <c r="BI1" s="46"/>
-      <c r="BJ1" s="46"/>
-      <c r="BK1" s="46"/>
-      <c r="BL1" s="46"/>
-      <c r="BM1" s="46"/>
-      <c r="BN1" s="46"/>
-      <c r="BO1" s="46"/>
-      <c r="BP1" s="46"/>
-      <c r="BQ1" s="46"/>
-      <c r="BR1" s="46"/>
-      <c r="BS1" s="46"/>
-      <c r="BT1" s="46"/>
-      <c r="BU1" s="46"/>
-      <c r="BV1" s="46"/>
-      <c r="BW1" s="46">
+      <c r="X1" s="20"/>
+      <c r="Y1" s="20"/>
+      <c r="Z1" s="20"/>
+      <c r="AA1" s="20"/>
+      <c r="AB1" s="20"/>
+      <c r="AC1" s="20"/>
+      <c r="AD1" s="20"/>
+      <c r="AE1" s="20"/>
+      <c r="AF1" s="20"/>
+      <c r="AG1" s="20"/>
+      <c r="AH1" s="20"/>
+      <c r="AI1" s="20"/>
+      <c r="AJ1" s="20"/>
+      <c r="AK1" s="20"/>
+      <c r="AL1" s="20"/>
+      <c r="AM1" s="20"/>
+      <c r="AN1" s="20"/>
+      <c r="AO1" s="20"/>
+      <c r="AP1" s="20"/>
+      <c r="AQ1" s="20"/>
+      <c r="AR1" s="20"/>
+      <c r="AS1" s="20"/>
+      <c r="AT1" s="20"/>
+      <c r="AU1" s="20"/>
+      <c r="AV1" s="20"/>
+      <c r="AW1" s="20"/>
+      <c r="AX1" s="20"/>
+      <c r="AY1" s="20"/>
+      <c r="AZ1" s="20"/>
+      <c r="BA1" s="20"/>
+      <c r="BB1" s="20"/>
+      <c r="BC1" s="20"/>
+      <c r="BD1" s="20"/>
+      <c r="BE1" s="20"/>
+      <c r="BF1" s="20"/>
+      <c r="BG1" s="20"/>
+      <c r="BH1" s="20"/>
+      <c r="BI1" s="20"/>
+      <c r="BJ1" s="20"/>
+      <c r="BK1" s="20"/>
+      <c r="BL1" s="20"/>
+      <c r="BM1" s="20"/>
+      <c r="BN1" s="20"/>
+      <c r="BO1" s="20"/>
+      <c r="BP1" s="20"/>
+      <c r="BQ1" s="20"/>
+      <c r="BR1" s="20"/>
+      <c r="BS1" s="20"/>
+      <c r="BT1" s="20"/>
+      <c r="BU1" s="20"/>
+      <c r="BV1" s="20"/>
+      <c r="BW1" s="20">
         <v>2028</v>
       </c>
-      <c r="BX1" s="46"/>
-      <c r="BY1" s="46"/>
-      <c r="BZ1" s="46"/>
-      <c r="CA1" s="46"/>
-      <c r="CB1" s="46"/>
-      <c r="CC1" s="46"/>
-      <c r="CD1" s="46"/>
-      <c r="CE1" s="46"/>
-      <c r="CF1" s="46"/>
-      <c r="CG1" s="46"/>
-      <c r="CH1" s="46"/>
-      <c r="CI1" s="46"/>
-      <c r="CJ1" s="46"/>
-      <c r="CK1" s="46"/>
-      <c r="CL1" s="46"/>
-      <c r="CM1" s="46"/>
+      <c r="BX1" s="20"/>
+      <c r="BY1" s="20"/>
+      <c r="BZ1" s="20"/>
+      <c r="CA1" s="20"/>
+      <c r="CB1" s="20"/>
+      <c r="CC1" s="20"/>
+      <c r="CD1" s="20"/>
+      <c r="CE1" s="20"/>
+      <c r="CF1" s="20"/>
+      <c r="CG1" s="20"/>
+      <c r="CH1" s="20"/>
+      <c r="CI1" s="20"/>
+      <c r="CJ1" s="20"/>
+      <c r="CK1" s="20"/>
+      <c r="CL1" s="20"/>
+      <c r="CM1" s="20"/>
     </row>
     <row r="2" spans="1:91" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D2" s="4"/>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="6" t="s">
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="7" t="s">
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="8" t="s">
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="8"/>
-      <c r="V2" s="8"/>
-      <c r="W2" s="9" t="s">
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="10" t="s">
+      <c r="X2" s="32"/>
+      <c r="Y2" s="32"/>
+      <c r="Z2" s="32"/>
+      <c r="AA2" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="AB2" s="10"/>
-      <c r="AC2" s="10"/>
-      <c r="AD2" s="10"/>
-      <c r="AE2" s="11" t="s">
+      <c r="AB2" s="24"/>
+      <c r="AC2" s="24"/>
+      <c r="AD2" s="24"/>
+      <c r="AE2" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="AF2" s="11"/>
-      <c r="AG2" s="11"/>
-      <c r="AH2" s="11"/>
-      <c r="AI2" s="11"/>
-      <c r="AJ2" s="12" t="s">
+      <c r="AF2" s="34"/>
+      <c r="AG2" s="34"/>
+      <c r="AH2" s="34"/>
+      <c r="AI2" s="34"/>
+      <c r="AJ2" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="AK2" s="12"/>
-      <c r="AL2" s="12"/>
-      <c r="AM2" s="12"/>
-      <c r="AN2" s="13" t="s">
+      <c r="AK2" s="44"/>
+      <c r="AL2" s="44"/>
+      <c r="AM2" s="44"/>
+      <c r="AN2" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="AO2" s="13"/>
-      <c r="AP2" s="13"/>
-      <c r="AQ2" s="13"/>
-      <c r="AR2" s="14" t="s">
+      <c r="AO2" s="25"/>
+      <c r="AP2" s="25"/>
+      <c r="AQ2" s="25"/>
+      <c r="AR2" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="AS2" s="14"/>
-      <c r="AT2" s="14"/>
-      <c r="AU2" s="14"/>
-      <c r="AV2" s="14"/>
-      <c r="AW2" s="15" t="s">
+      <c r="AS2" s="40"/>
+      <c r="AT2" s="40"/>
+      <c r="AU2" s="40"/>
+      <c r="AV2" s="40"/>
+      <c r="AW2" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="AX2" s="15"/>
-      <c r="AY2" s="15"/>
-      <c r="AZ2" s="15"/>
-      <c r="BA2" s="16" t="s">
+      <c r="AX2" s="39"/>
+      <c r="AY2" s="39"/>
+      <c r="AZ2" s="39"/>
+      <c r="BA2" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="BB2" s="16"/>
-      <c r="BC2" s="16"/>
-      <c r="BD2" s="16"/>
-      <c r="BE2" s="16"/>
-      <c r="BF2" s="5" t="s">
+      <c r="BB2" s="38"/>
+      <c r="BC2" s="38"/>
+      <c r="BD2" s="38"/>
+      <c r="BE2" s="38"/>
+      <c r="BF2" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="BG2" s="5"/>
-      <c r="BH2" s="5"/>
-      <c r="BI2" s="5"/>
-      <c r="BJ2" s="6" t="s">
+      <c r="BG2" s="21"/>
+      <c r="BH2" s="21"/>
+      <c r="BI2" s="21"/>
+      <c r="BJ2" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="BK2" s="6"/>
-      <c r="BL2" s="6"/>
-      <c r="BM2" s="6"/>
-      <c r="BN2" s="7" t="s">
+      <c r="BK2" s="22"/>
+      <c r="BL2" s="22"/>
+      <c r="BM2" s="22"/>
+      <c r="BN2" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="BO2" s="7"/>
-      <c r="BP2" s="7"/>
-      <c r="BQ2" s="7"/>
-      <c r="BR2" s="7"/>
-      <c r="BS2" s="8" t="s">
+      <c r="BO2" s="23"/>
+      <c r="BP2" s="23"/>
+      <c r="BQ2" s="23"/>
+      <c r="BR2" s="23"/>
+      <c r="BS2" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="BT2" s="8"/>
-      <c r="BU2" s="8"/>
-      <c r="BV2" s="8"/>
-      <c r="BW2" s="9" t="s">
+      <c r="BT2" s="31"/>
+      <c r="BU2" s="31"/>
+      <c r="BV2" s="31"/>
+      <c r="BW2" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="BX2" s="9"/>
-      <c r="BY2" s="9"/>
-      <c r="BZ2" s="9"/>
-      <c r="CA2" s="10" t="s">
+      <c r="BX2" s="32"/>
+      <c r="BY2" s="32"/>
+      <c r="BZ2" s="32"/>
+      <c r="CA2" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="CB2" s="10"/>
-      <c r="CC2" s="10"/>
-      <c r="CD2" s="10"/>
-      <c r="CE2" s="10"/>
-      <c r="CF2" s="11" t="s">
+      <c r="CB2" s="24"/>
+      <c r="CC2" s="24"/>
+      <c r="CD2" s="24"/>
+      <c r="CE2" s="24"/>
+      <c r="CF2" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="CG2" s="11"/>
-      <c r="CH2" s="11"/>
-      <c r="CI2" s="11"/>
-      <c r="CJ2" s="12" t="s">
+      <c r="CG2" s="34"/>
+      <c r="CH2" s="34"/>
+      <c r="CI2" s="34"/>
+      <c r="CJ2" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="CK2" s="12"/>
-      <c r="CL2" s="12"/>
-      <c r="CM2" s="12"/>
+      <c r="CK2" s="44"/>
+      <c r="CL2" s="44"/>
+      <c r="CM2" s="44"/>
     </row>
-    <row r="3" spans="1:91" s="17" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D3" s="18"/>
-      <c r="E3" s="19">
+    <row r="3" spans="1:91" s="5" customFormat="1" ht="33" customHeight="1" collapsed="1" x14ac:dyDescent="0.4">
+      <c r="D3" s="6"/>
+      <c r="E3" s="26">
         <f>SUM(E4:H4)</f>
         <v>0</v>
       </c>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="20">
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="29">
         <f>SUM(I4:M4)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="21">
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="28">
         <f>SUM(N4:Q4)</f>
         <v>0</v>
       </c>
-      <c r="O3" s="21"/>
-      <c r="P3" s="21"/>
-      <c r="Q3" s="21"/>
-      <c r="R3" s="22">
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="28"/>
+      <c r="R3" s="30">
         <f>SUM(R4:V4)</f>
         <v>0</v>
       </c>
-      <c r="S3" s="22"/>
-      <c r="T3" s="22"/>
-      <c r="U3" s="22"/>
-      <c r="V3" s="22"/>
-      <c r="W3" s="23">
+      <c r="S3" s="30"/>
+      <c r="T3" s="30"/>
+      <c r="U3" s="30"/>
+      <c r="V3" s="30"/>
+      <c r="W3" s="33">
         <f>SUM(W4:Z4)</f>
         <v>0</v>
       </c>
-      <c r="X3" s="23"/>
-      <c r="Y3" s="23"/>
-      <c r="Z3" s="23"/>
-      <c r="AA3" s="24">
+      <c r="X3" s="33"/>
+      <c r="Y3" s="33"/>
+      <c r="Z3" s="33"/>
+      <c r="AA3" s="27">
         <f>SUM(AA4:AD4)</f>
         <v>0</v>
       </c>
-      <c r="AB3" s="24"/>
-      <c r="AC3" s="24"/>
-      <c r="AD3" s="24"/>
-      <c r="AE3" s="25">
+      <c r="AB3" s="27"/>
+      <c r="AC3" s="27"/>
+      <c r="AD3" s="27"/>
+      <c r="AE3" s="35">
         <f>SUM(AE4:AI4)</f>
         <v>0</v>
       </c>
-      <c r="AF3" s="25"/>
-      <c r="AG3" s="25"/>
-      <c r="AH3" s="25"/>
-      <c r="AI3" s="25"/>
-      <c r="AJ3" s="26">
+      <c r="AF3" s="35"/>
+      <c r="AG3" s="35"/>
+      <c r="AH3" s="35"/>
+      <c r="AI3" s="35"/>
+      <c r="AJ3" s="43">
         <f>SUM(AJ4:AM4)</f>
         <v>0</v>
       </c>
-      <c r="AK3" s="26"/>
-      <c r="AL3" s="26"/>
-      <c r="AM3" s="26"/>
-      <c r="AN3" s="27">
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="42">
         <f>SUM(AN4:AQ4)</f>
         <v>0</v>
       </c>
-      <c r="AO3" s="27"/>
-      <c r="AP3" s="27"/>
-      <c r="AQ3" s="27"/>
-      <c r="AR3" s="28">
+      <c r="AO3" s="42"/>
+      <c r="AP3" s="42"/>
+      <c r="AQ3" s="42"/>
+      <c r="AR3" s="41">
         <f>SUM(AR4:AV4)</f>
         <v>0</v>
       </c>
-      <c r="AS3" s="28"/>
-      <c r="AT3" s="28"/>
-      <c r="AU3" s="28"/>
-      <c r="AV3" s="28"/>
-      <c r="AW3" s="29">
+      <c r="AS3" s="41"/>
+      <c r="AT3" s="41"/>
+      <c r="AU3" s="41"/>
+      <c r="AV3" s="41"/>
+      <c r="AW3" s="37">
         <f>SUM(AW4:AZ4)</f>
         <v>0</v>
       </c>
-      <c r="AX3" s="29"/>
-      <c r="AY3" s="29"/>
-      <c r="AZ3" s="29"/>
-      <c r="BA3" s="30">
+      <c r="AX3" s="37"/>
+      <c r="AY3" s="37"/>
+      <c r="AZ3" s="37"/>
+      <c r="BA3" s="36">
         <f>SUM(BA4:BE4)</f>
         <v>0</v>
       </c>
-      <c r="BB3" s="30"/>
-      <c r="BC3" s="30"/>
-      <c r="BD3" s="30"/>
-      <c r="BE3" s="30"/>
-      <c r="BF3" s="19">
+      <c r="BB3" s="36"/>
+      <c r="BC3" s="36"/>
+      <c r="BD3" s="36"/>
+      <c r="BE3" s="36"/>
+      <c r="BF3" s="26">
         <f>SUM(BF4:BI4)</f>
         <v>0</v>
       </c>
-      <c r="BG3" s="19"/>
-      <c r="BH3" s="19"/>
-      <c r="BI3" s="19"/>
-      <c r="BJ3" s="20">
+      <c r="BG3" s="26"/>
+      <c r="BH3" s="26"/>
+      <c r="BI3" s="26"/>
+      <c r="BJ3" s="29">
         <f>SUM(BJ4:BM4)</f>
         <v>0</v>
       </c>
-      <c r="BK3" s="20"/>
-      <c r="BL3" s="20"/>
-      <c r="BM3" s="20"/>
-      <c r="BN3" s="21">
+      <c r="BK3" s="29"/>
+      <c r="BL3" s="29"/>
+      <c r="BM3" s="29"/>
+      <c r="BN3" s="28">
         <f>SUM(BN4:BR4)</f>
         <v>0</v>
       </c>
-      <c r="BO3" s="21"/>
-      <c r="BP3" s="21"/>
-      <c r="BQ3" s="21"/>
-      <c r="BR3" s="21"/>
-      <c r="BS3" s="22">
+      <c r="BO3" s="28"/>
+      <c r="BP3" s="28"/>
+      <c r="BQ3" s="28"/>
+      <c r="BR3" s="28"/>
+      <c r="BS3" s="30">
         <f>SUM(BS4:BV4)</f>
         <v>0</v>
       </c>
-      <c r="BT3" s="22"/>
-      <c r="BU3" s="22"/>
-      <c r="BV3" s="22"/>
-      <c r="BW3" s="23">
+      <c r="BT3" s="30"/>
+      <c r="BU3" s="30"/>
+      <c r="BV3" s="30"/>
+      <c r="BW3" s="33">
         <f>SUM(BW4:BZ4)</f>
         <v>0</v>
       </c>
-      <c r="BX3" s="23"/>
-      <c r="BY3" s="23"/>
-      <c r="BZ3" s="23"/>
-      <c r="CA3" s="24">
+      <c r="BX3" s="33"/>
+      <c r="BY3" s="33"/>
+      <c r="BZ3" s="33"/>
+      <c r="CA3" s="27">
         <f>SUM(CA4:CE4)</f>
         <v>0</v>
       </c>
-      <c r="CB3" s="24"/>
-      <c r="CC3" s="24"/>
-      <c r="CD3" s="24"/>
-      <c r="CE3" s="24"/>
-      <c r="CF3" s="25">
+      <c r="CB3" s="27"/>
+      <c r="CC3" s="27"/>
+      <c r="CD3" s="27"/>
+      <c r="CE3" s="27"/>
+      <c r="CF3" s="35">
         <f>SUM(CF4:CI4)</f>
         <v>0</v>
       </c>
-      <c r="CG3" s="25"/>
-      <c r="CH3" s="25"/>
-      <c r="CI3" s="25"/>
-      <c r="CJ3" s="26">
+      <c r="CG3" s="35"/>
+      <c r="CH3" s="35"/>
+      <c r="CI3" s="35"/>
+      <c r="CJ3" s="43">
         <f>SUM(CJ4:CM4)</f>
         <v>0</v>
       </c>
-      <c r="CK3" s="26"/>
-      <c r="CL3" s="26"/>
-      <c r="CM3" s="26"/>
+      <c r="CK3" s="43"/>
+      <c r="CL3" s="43"/>
+      <c r="CM3" s="43"/>
     </row>
-    <row r="4" spans="1:91" s="17" customFormat="1" ht="16.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D4" s="31" t="s">
+    <row r="4" spans="1:91" s="5" customFormat="1" ht="16.5" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="D4" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="32">
+      <c r="E4" s="8">
         <f t="shared" ref="E4:AJ4" si="0">E5 + E6</f>
         <v>0</v>
       </c>
-      <c r="F4" s="32">
+      <c r="F4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G4" s="32">
+      <c r="G4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H4" s="32">
+      <c r="H4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K4" s="32">
+      <c r="K4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M4" s="32">
+      <c r="M4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N4" s="32">
+      <c r="N4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O4" s="32">
+      <c r="O4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P4" s="32">
+      <c r="P4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q4" s="32">
+      <c r="Q4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S4" s="32">
+      <c r="S4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="T4" s="32">
+      <c r="T4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U4" s="32">
+      <c r="U4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V4" s="32">
+      <c r="V4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W4" s="32">
+      <c r="W4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X4" s="32">
+      <c r="X4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y4" s="32">
+      <c r="Y4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Z4" s="32">
+      <c r="Z4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA4" s="32">
+      <c r="AA4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AB4" s="32">
+      <c r="AB4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AC4" s="32">
+      <c r="AC4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AD4" s="32">
+      <c r="AD4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AE4" s="32">
+      <c r="AE4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AF4" s="32">
+      <c r="AF4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AG4" s="32">
+      <c r="AG4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH4" s="32">
+      <c r="AH4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AI4" s="32">
+      <c r="AI4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AJ4" s="32">
+      <c r="AJ4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AK4" s="32">
+      <c r="AK4" s="8">
         <f t="shared" ref="AK4:CK4" si="1">AK5 + AK6</f>
         <v>0</v>
       </c>
-      <c r="AL4" s="32">
+      <c r="AL4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AM4" s="32">
+      <c r="AM4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN4" s="32">
+      <c r="AN4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO4" s="32">
+      <c r="AO4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AP4" s="32">
+      <c r="AP4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AQ4" s="32">
+      <c r="AQ4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AR4" s="32">
+      <c r="AR4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AS4" s="32">
+      <c r="AS4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AT4" s="32">
+      <c r="AT4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AU4" s="32">
+      <c r="AU4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AV4" s="32">
+      <c r="AV4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AW4" s="32">
+      <c r="AW4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AX4" s="32">
+      <c r="AX4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AY4" s="32">
+      <c r="AY4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AZ4" s="32">
+      <c r="AZ4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BA4" s="32">
+      <c r="BA4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BB4" s="32">
+      <c r="BB4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BC4" s="32">
+      <c r="BC4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BD4" s="32">
+      <c r="BD4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BE4" s="32">
+      <c r="BE4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BF4" s="32">
+      <c r="BF4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BG4" s="32">
+      <c r="BG4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BH4" s="32">
+      <c r="BH4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BI4" s="32">
+      <c r="BI4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BJ4" s="32">
+      <c r="BJ4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BK4" s="32">
+      <c r="BK4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BL4" s="32">
+      <c r="BL4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BM4" s="32">
+      <c r="BM4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BN4" s="32">
+      <c r="BN4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BO4" s="32">
+      <c r="BO4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BP4" s="32">
+      <c r="BP4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BQ4" s="32">
+      <c r="BQ4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BR4" s="32">
+      <c r="BR4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BS4" s="32">
+      <c r="BS4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BT4" s="32">
+      <c r="BT4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BU4" s="32">
+      <c r="BU4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BV4" s="32">
+      <c r="BV4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BW4" s="32">
+      <c r="BW4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BX4" s="32">
+      <c r="BX4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BY4" s="32">
+      <c r="BY4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BZ4" s="32">
+      <c r="BZ4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CA4" s="32">
+      <c r="CA4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CB4" s="32">
+      <c r="CB4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CC4" s="32">
+      <c r="CC4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CD4" s="32">
+      <c r="CD4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CE4" s="32">
+      <c r="CE4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CF4" s="32">
+      <c r="CF4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CG4" s="32">
+      <c r="CG4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CH4" s="32">
+      <c r="CH4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CI4" s="32">
+      <c r="CI4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CJ4" s="32">
+      <c r="CJ4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CK4" s="32">
+      <c r="CK4" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CL4" s="32">
+      <c r="CL4" s="8">
         <f t="shared" ref="CL4:CM4" si="2">CL5 + CL6</f>
         <v>0</v>
       </c>
-      <c r="CM4" s="32">
+      <c r="CM4" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:91" s="33" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D5" s="31" t="s">
+    <row r="5" spans="1:91" s="9" customFormat="1" ht="16.5" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="D5" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="34">
+      <c r="E5" s="10">
         <f t="shared" ref="E5:AJ5" si="3">SUMIFS(E9:E90, $A9:$A90, $D5, $B9:$B90, 1) * 1</f>
         <v>0</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G5" s="34">
+      <c r="G5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H5" s="34">
+      <c r="H5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I5" s="34">
+      <c r="I5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J5" s="34">
+      <c r="J5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K5" s="34">
+      <c r="K5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L5" s="34">
+      <c r="L5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M5" s="34">
+      <c r="M5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N5" s="34">
+      <c r="N5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O5" s="34">
+      <c r="O5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P5" s="34">
+      <c r="P5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q5" s="34">
+      <c r="Q5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R5" s="34">
+      <c r="R5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S5" s="34">
+      <c r="S5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T5" s="34">
+      <c r="T5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U5" s="34">
+      <c r="U5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V5" s="34">
+      <c r="V5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W5" s="34">
+      <c r="W5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X5" s="34">
+      <c r="X5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y5" s="34">
+      <c r="Y5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z5" s="34">
+      <c r="Z5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA5" s="34">
+      <c r="AA5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB5" s="34">
+      <c r="AB5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC5" s="34">
+      <c r="AC5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AD5" s="34">
+      <c r="AD5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE5" s="34">
+      <c r="AE5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AF5" s="34">
+      <c r="AF5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AG5" s="34">
+      <c r="AG5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AH5" s="34">
+      <c r="AH5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI5" s="34">
+      <c r="AI5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AJ5" s="34">
+      <c r="AJ5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AK5" s="34">
+      <c r="AK5" s="10">
         <f t="shared" ref="AK5:CK5" si="4">SUMIFS(AK9:AK90, $A9:$A90, $D5, $B9:$B90, 1) * 1</f>
         <v>0</v>
       </c>
-      <c r="AL5" s="34">
+      <c r="AL5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AM5" s="34">
+      <c r="AM5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AN5" s="34">
+      <c r="AN5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AO5" s="34">
+      <c r="AO5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AP5" s="34">
+      <c r="AP5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AQ5" s="34">
+      <c r="AQ5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AR5" s="34">
+      <c r="AR5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AS5" s="34">
+      <c r="AS5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AT5" s="34">
+      <c r="AT5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AU5" s="34">
+      <c r="AU5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AV5" s="34">
+      <c r="AV5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AW5" s="34">
+      <c r="AW5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AX5" s="34">
+      <c r="AX5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AY5" s="34">
+      <c r="AY5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AZ5" s="34">
+      <c r="AZ5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA5" s="34">
+      <c r="BA5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BB5" s="34">
+      <c r="BB5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BC5" s="34">
+      <c r="BC5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BD5" s="34">
+      <c r="BD5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BE5" s="34">
+      <c r="BE5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BF5" s="34">
+      <c r="BF5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BG5" s="34">
+      <c r="BG5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BH5" s="34">
+      <c r="BH5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BI5" s="34">
+      <c r="BI5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BJ5" s="34">
+      <c r="BJ5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BK5" s="34">
+      <c r="BK5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BL5" s="34">
+      <c r="BL5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BM5" s="34">
+      <c r="BM5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BN5" s="34">
+      <c r="BN5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BO5" s="34">
+      <c r="BO5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BP5" s="34">
+      <c r="BP5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BQ5" s="34">
+      <c r="BQ5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BR5" s="34">
+      <c r="BR5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BS5" s="34">
+      <c r="BS5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BT5" s="34">
+      <c r="BT5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BU5" s="34">
+      <c r="BU5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BV5" s="34">
+      <c r="BV5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BW5" s="34">
+      <c r="BW5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BX5" s="34">
+      <c r="BX5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BY5" s="34">
+      <c r="BY5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BZ5" s="34">
+      <c r="BZ5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="CA5" s="34">
+      <c r="CA5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="CB5" s="34">
+      <c r="CB5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="CC5" s="34">
+      <c r="CC5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="CD5" s="34">
+      <c r="CD5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="CE5" s="34">
+      <c r="CE5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="CF5" s="34">
+      <c r="CF5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="CG5" s="34">
+      <c r="CG5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="CH5" s="34">
+      <c r="CH5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="CI5" s="34">
+      <c r="CI5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="CJ5" s="34">
+      <c r="CJ5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="CK5" s="34">
+      <c r="CK5" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="CL5" s="34">
+      <c r="CL5" s="10">
         <f t="shared" ref="CL5:CM5" si="5">SUMIFS(CL9:CL90, $A9:$A90, $D5, $B9:$B90, 1) * 1</f>
         <v>0</v>
       </c>
-      <c r="CM5" s="34">
+      <c r="CM5" s="10">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:91" s="33" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="D6" s="31" t="s">
+    <row r="6" spans="1:91" s="9" customFormat="1" ht="16.5" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="D6" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="35">
+      <c r="E6" s="11">
         <f t="shared" ref="E6:AJ6" si="6">SUMIFS(E9:E90, $A9:$A90, $D6, $B9:$B90, 1) * -1</f>
         <v>0</v>
       </c>
-      <c r="F6" s="35">
+      <c r="F6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G6" s="35">
+      <c r="G6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H6" s="35">
+      <c r="H6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I6" s="35">
+      <c r="I6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J6" s="35">
+      <c r="J6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="K6" s="35">
+      <c r="K6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="L6" s="35">
+      <c r="L6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="M6" s="35">
+      <c r="M6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="N6" s="35">
+      <c r="N6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O6" s="35">
+      <c r="O6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="P6" s="35">
+      <c r="P6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q6" s="35">
+      <c r="Q6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R6" s="35">
+      <c r="R6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="S6" s="35">
+      <c r="S6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T6" s="35">
+      <c r="T6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U6" s="35">
+      <c r="U6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="V6" s="35">
+      <c r="V6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W6" s="35">
+      <c r="W6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="X6" s="35">
+      <c r="X6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Y6" s="35">
+      <c r="Y6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z6" s="35">
+      <c r="Z6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA6" s="35">
+      <c r="AA6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB6" s="35">
+      <c r="AB6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AC6" s="35">
+      <c r="AC6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AD6" s="35">
+      <c r="AD6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AE6" s="35">
+      <c r="AE6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AF6" s="35">
+      <c r="AF6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AG6" s="35">
+      <c r="AG6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AH6" s="35">
+      <c r="AH6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI6" s="35">
+      <c r="AI6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AJ6" s="35">
+      <c r="AJ6" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AK6" s="35">
+      <c r="AK6" s="11">
         <f t="shared" ref="AK6:CK6" si="7">SUMIFS(AK9:AK90, $A9:$A90, $D6, $B9:$B90, 1) * -1</f>
         <v>0</v>
       </c>
-      <c r="AL6" s="35">
+      <c r="AL6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM6" s="35">
+      <c r="AM6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AN6" s="35">
+      <c r="AN6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AO6" s="35">
+      <c r="AO6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AP6" s="35">
+      <c r="AP6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AQ6" s="35">
+      <c r="AQ6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AR6" s="35">
+      <c r="AR6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AS6" s="35">
+      <c r="AS6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AT6" s="35">
+      <c r="AT6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AU6" s="35">
+      <c r="AU6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AV6" s="35">
+      <c r="AV6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AW6" s="35">
+      <c r="AW6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AX6" s="35">
+      <c r="AX6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AY6" s="35">
+      <c r="AY6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AZ6" s="35">
+      <c r="AZ6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BA6" s="35">
+      <c r="BA6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BB6" s="35">
+      <c r="BB6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BC6" s="35">
+      <c r="BC6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BD6" s="35">
+      <c r="BD6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BE6" s="35">
+      <c r="BE6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BF6" s="35">
+      <c r="BF6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BG6" s="35">
+      <c r="BG6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BH6" s="35">
+      <c r="BH6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BI6" s="35">
+      <c r="BI6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BJ6" s="35">
+      <c r="BJ6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BK6" s="35">
+      <c r="BK6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BL6" s="35">
+      <c r="BL6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BM6" s="35">
+      <c r="BM6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BN6" s="35">
+      <c r="BN6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BO6" s="35">
+      <c r="BO6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BP6" s="35">
+      <c r="BP6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BQ6" s="35">
+      <c r="BQ6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BR6" s="35">
+      <c r="BR6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BS6" s="35">
+      <c r="BS6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BT6" s="35">
+      <c r="BT6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BU6" s="35">
+      <c r="BU6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BV6" s="35">
+      <c r="BV6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BW6" s="35">
+      <c r="BW6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BX6" s="35">
+      <c r="BX6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BY6" s="35">
+      <c r="BY6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BZ6" s="35">
+      <c r="BZ6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="CA6" s="35">
+      <c r="CA6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="CB6" s="35">
+      <c r="CB6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="CC6" s="35">
+      <c r="CC6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="CD6" s="35">
+      <c r="CD6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="CE6" s="35">
+      <c r="CE6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="CF6" s="35">
+      <c r="CF6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="CG6" s="35">
+      <c r="CG6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="CH6" s="35">
+      <c r="CH6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="CI6" s="35">
+      <c r="CI6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="CJ6" s="35">
+      <c r="CJ6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="CK6" s="35">
+      <c r="CK6" s="11">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="CL6" s="35">
+      <c r="CL6" s="11">
         <f t="shared" ref="CL6:CM6" si="8">SUMIFS(CL9:CL90, $A9:$A90, $D6, $B9:$B90, 1) * -1</f>
         <v>0</v>
       </c>
-      <c r="CM6" s="35">
+      <c r="CM6" s="11">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:91" s="36" customFormat="1" ht="0.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D7" s="37" t="s">
+    <row r="7" spans="1:91" s="45" customFormat="1" ht="16.5" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="E7" s="36">
+      <c r="E7" s="45">
         <f>E4</f>
         <v>0</v>
       </c>
-      <c r="F7" s="36">
+      <c r="F7" s="45">
         <f t="shared" ref="F7:AK7" si="9">E7+F4</f>
         <v>0</v>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="H7" s="36">
+      <c r="H7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="I7" s="36">
+      <c r="I7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J7" s="36">
+      <c r="J7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="K7" s="36">
+      <c r="K7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="L7" s="36">
+      <c r="L7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="M7" s="36">
+      <c r="M7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="N7" s="36">
+      <c r="N7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="O7" s="36">
+      <c r="O7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="P7" s="36">
+      <c r="P7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Q7" s="36">
+      <c r="Q7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="R7" s="36">
+      <c r="R7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="S7" s="36">
+      <c r="S7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T7" s="36">
+      <c r="T7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U7" s="36">
+      <c r="U7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="V7" s="36">
+      <c r="V7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="W7" s="36">
+      <c r="W7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="X7" s="36">
+      <c r="X7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Y7" s="36">
+      <c r="Y7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Z7" s="36">
+      <c r="Z7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AA7" s="36">
+      <c r="AA7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AB7" s="36">
+      <c r="AB7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AC7" s="36">
+      <c r="AC7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AD7" s="36">
+      <c r="AD7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AE7" s="36">
+      <c r="AE7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AF7" s="36">
+      <c r="AF7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AG7" s="36">
+      <c r="AG7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AH7" s="36">
+      <c r="AH7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AI7" s="36">
+      <c r="AI7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AJ7" s="36">
+      <c r="AJ7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AK7" s="36">
+      <c r="AK7" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL7" s="36">
-        <f t="shared" ref="AL7:BE7" si="10">AK7+AL4</f>
-        <v>0</v>
-      </c>
-      <c r="AM7" s="36">
+      <c r="AL7" s="45">
+        <f t="shared" ref="AL7:BF7" si="10">AK7+AL4</f>
+        <v>0</v>
+      </c>
+      <c r="AM7" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AN7" s="36">
+      <c r="AN7" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AO7" s="36">
+      <c r="AO7" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AP7" s="36">
+      <c r="AP7" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AQ7" s="36">
+      <c r="AQ7" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR7" s="36">
+      <c r="AR7" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AS7" s="36">
+      <c r="AS7" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AT7" s="36">
+      <c r="AT7" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AU7" s="36">
+      <c r="AU7" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AV7" s="36">
+      <c r="AV7" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AW7" s="36">
+      <c r="AW7" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AX7" s="36">
+      <c r="AX7" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AY7" s="36">
+      <c r="AY7" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AZ7" s="36">
+      <c r="AZ7" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BA7" s="36">
+      <c r="BA7" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BB7" s="36">
+      <c r="BB7" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BC7" s="36">
+      <c r="BC7" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BD7" s="36">
+      <c r="BD7" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BE7" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="BF7" s="36">
-        <f>BF4</f>
-        <v>0</v>
-      </c>
-      <c r="BG7" s="36">
-        <f t="shared" ref="BG7" si="11">BF7+BG4</f>
-        <v>0</v>
-      </c>
-      <c r="BH7" s="36">
-        <f t="shared" ref="BH7" si="12">BG7+BH4</f>
-        <v>0</v>
-      </c>
-      <c r="BI7" s="36">
-        <f t="shared" ref="BI7" si="13">BH7+BI4</f>
-        <v>0</v>
-      </c>
-      <c r="BJ7" s="36">
-        <f t="shared" ref="BJ7" si="14">BI7+BJ4</f>
-        <v>0</v>
-      </c>
-      <c r="BK7" s="36">
-        <f t="shared" ref="BK7" si="15">BJ7+BK4</f>
-        <v>0</v>
-      </c>
-      <c r="BL7" s="36">
-        <f t="shared" ref="BL7" si="16">BK7+BL4</f>
-        <v>0</v>
-      </c>
-      <c r="BM7" s="36">
-        <f t="shared" ref="BM7" si="17">BL7+BM4</f>
-        <v>0</v>
-      </c>
-      <c r="BN7" s="36">
-        <f t="shared" ref="BN7" si="18">BM7+BN4</f>
-        <v>0</v>
-      </c>
-      <c r="BO7" s="36">
-        <f t="shared" ref="BO7" si="19">BN7+BO4</f>
-        <v>0</v>
-      </c>
-      <c r="BP7" s="36">
-        <f t="shared" ref="BP7" si="20">BO7+BP4</f>
-        <v>0</v>
-      </c>
-      <c r="BQ7" s="36">
-        <f t="shared" ref="BQ7" si="21">BP7+BQ4</f>
-        <v>0</v>
-      </c>
-      <c r="BR7" s="36">
-        <f t="shared" ref="BR7" si="22">BQ7+BR4</f>
-        <v>0</v>
-      </c>
-      <c r="BS7" s="36">
-        <f t="shared" ref="BS7" si="23">BR7+BS4</f>
-        <v>0</v>
-      </c>
-      <c r="BT7" s="36">
-        <f t="shared" ref="BT7" si="24">BS7+BT4</f>
-        <v>0</v>
-      </c>
-      <c r="BU7" s="36">
-        <f t="shared" ref="BU7" si="25">BT7+BU4</f>
-        <v>0</v>
-      </c>
-      <c r="BV7" s="36">
-        <f t="shared" ref="BV7" si="26">BU7+BV4</f>
-        <v>0</v>
-      </c>
-      <c r="BW7" s="36">
-        <f t="shared" ref="BW7" si="27">BV7+BW4</f>
-        <v>0</v>
-      </c>
-      <c r="BX7" s="36">
-        <f t="shared" ref="BX7" si="28">BW7+BX4</f>
-        <v>0</v>
-      </c>
-      <c r="BY7" s="36">
-        <f t="shared" ref="BY7" si="29">BX7+BY4</f>
-        <v>0</v>
-      </c>
-      <c r="BZ7" s="36">
-        <f t="shared" ref="BZ7" si="30">BY7+BZ4</f>
-        <v>0</v>
-      </c>
-      <c r="CA7" s="36">
-        <f t="shared" ref="CA7" si="31">BZ7+CA4</f>
-        <v>0</v>
-      </c>
-      <c r="CB7" s="36">
-        <f t="shared" ref="CB7" si="32">CA7+CB4</f>
-        <v>0</v>
-      </c>
-      <c r="CC7" s="36">
-        <f t="shared" ref="CC7" si="33">CB7+CC4</f>
-        <v>0</v>
-      </c>
-      <c r="CD7" s="36">
-        <f t="shared" ref="CD7" si="34">CC7+CD4</f>
-        <v>0</v>
-      </c>
-      <c r="CE7" s="36">
-        <f t="shared" ref="CE7" si="35">CD7+CE4</f>
-        <v>0</v>
-      </c>
-      <c r="CF7" s="36">
-        <f t="shared" ref="CF7" si="36">CE7+CF4</f>
-        <v>0</v>
-      </c>
-      <c r="CG7" s="36">
-        <f t="shared" ref="CG7" si="37">CF7+CG4</f>
-        <v>0</v>
-      </c>
-      <c r="CH7" s="36">
-        <f t="shared" ref="CH7" si="38">CG7+CH4</f>
-        <v>0</v>
-      </c>
-      <c r="CI7" s="36">
-        <f t="shared" ref="CI7" si="39">CH7+CI4</f>
-        <v>0</v>
-      </c>
-      <c r="CJ7" s="36">
-        <f t="shared" ref="CJ7" si="40">CI7+CJ4</f>
-        <v>0</v>
-      </c>
-      <c r="CK7" s="36">
-        <f t="shared" ref="CK7" si="41">CJ7+CK4</f>
-        <v>0</v>
-      </c>
-      <c r="CL7" s="36">
-        <f t="shared" ref="CL7" si="42">CK7+CL4</f>
-        <v>0</v>
-      </c>
-      <c r="CM7" s="36">
-        <f t="shared" ref="CM7" si="43">CL7+CM4</f>
+      <c r="BE7" s="45">
+        <f>BD7+BE4</f>
+        <v>0</v>
+      </c>
+      <c r="BF7" s="45">
+        <f>BE7+BF4</f>
+        <v>0</v>
+      </c>
+      <c r="BG7" s="45">
+        <f>BF7+BG4</f>
+        <v>0</v>
+      </c>
+      <c r="BH7" s="45">
+        <f t="shared" ref="BH7" si="11">BG7+BH4</f>
+        <v>0</v>
+      </c>
+      <c r="BI7" s="45">
+        <f t="shared" ref="BI7" si="12">BH7+BI4</f>
+        <v>0</v>
+      </c>
+      <c r="BJ7" s="45">
+        <f t="shared" ref="BJ7" si="13">BI7+BJ4</f>
+        <v>0</v>
+      </c>
+      <c r="BK7" s="45">
+        <f t="shared" ref="BK7" si="14">BJ7+BK4</f>
+        <v>0</v>
+      </c>
+      <c r="BL7" s="45">
+        <f t="shared" ref="BL7" si="15">BK7+BL4</f>
+        <v>0</v>
+      </c>
+      <c r="BM7" s="45">
+        <f t="shared" ref="BM7" si="16">BL7+BM4</f>
+        <v>0</v>
+      </c>
+      <c r="BN7" s="45">
+        <f t="shared" ref="BN7" si="17">BM7+BN4</f>
+        <v>0</v>
+      </c>
+      <c r="BO7" s="45">
+        <f t="shared" ref="BO7" si="18">BN7+BO4</f>
+        <v>0</v>
+      </c>
+      <c r="BP7" s="45">
+        <f t="shared" ref="BP7" si="19">BO7+BP4</f>
+        <v>0</v>
+      </c>
+      <c r="BQ7" s="45">
+        <f t="shared" ref="BQ7" si="20">BP7+BQ4</f>
+        <v>0</v>
+      </c>
+      <c r="BR7" s="45">
+        <f t="shared" ref="BR7" si="21">BQ7+BR4</f>
+        <v>0</v>
+      </c>
+      <c r="BS7" s="45">
+        <f t="shared" ref="BS7" si="22">BR7+BS4</f>
+        <v>0</v>
+      </c>
+      <c r="BT7" s="45">
+        <f t="shared" ref="BT7" si="23">BS7+BT4</f>
+        <v>0</v>
+      </c>
+      <c r="BU7" s="45">
+        <f t="shared" ref="BU7" si="24">BT7+BU4</f>
+        <v>0</v>
+      </c>
+      <c r="BV7" s="45">
+        <f t="shared" ref="BV7" si="25">BU7+BV4</f>
+        <v>0</v>
+      </c>
+      <c r="BW7" s="45">
+        <f t="shared" ref="BW7" si="26">BV7+BW4</f>
+        <v>0</v>
+      </c>
+      <c r="BX7" s="45">
+        <f t="shared" ref="BX7" si="27">BW7+BX4</f>
+        <v>0</v>
+      </c>
+      <c r="BY7" s="45">
+        <f t="shared" ref="BY7" si="28">BX7+BY4</f>
+        <v>0</v>
+      </c>
+      <c r="BZ7" s="45">
+        <f t="shared" ref="BZ7" si="29">BY7+BZ4</f>
+        <v>0</v>
+      </c>
+      <c r="CA7" s="45">
+        <f t="shared" ref="CA7" si="30">BZ7+CA4</f>
+        <v>0</v>
+      </c>
+      <c r="CB7" s="45">
+        <f t="shared" ref="CB7" si="31">CA7+CB4</f>
+        <v>0</v>
+      </c>
+      <c r="CC7" s="45">
+        <f t="shared" ref="CC7" si="32">CB7+CC4</f>
+        <v>0</v>
+      </c>
+      <c r="CD7" s="45">
+        <f t="shared" ref="CD7" si="33">CC7+CD4</f>
+        <v>0</v>
+      </c>
+      <c r="CE7" s="45">
+        <f t="shared" ref="CE7" si="34">CD7+CE4</f>
+        <v>0</v>
+      </c>
+      <c r="CF7" s="45">
+        <f t="shared" ref="CF7" si="35">CE7+CF4</f>
+        <v>0</v>
+      </c>
+      <c r="CG7" s="45">
+        <f t="shared" ref="CG7" si="36">CF7+CG4</f>
+        <v>0</v>
+      </c>
+      <c r="CH7" s="45">
+        <f t="shared" ref="CH7" si="37">CG7+CH4</f>
+        <v>0</v>
+      </c>
+      <c r="CI7" s="45">
+        <f t="shared" ref="CI7" si="38">CH7+CI4</f>
+        <v>0</v>
+      </c>
+      <c r="CJ7" s="45">
+        <f t="shared" ref="CJ7" si="39">CI7+CJ4</f>
+        <v>0</v>
+      </c>
+      <c r="CK7" s="45">
+        <f t="shared" ref="CK7" si="40">CJ7+CK4</f>
+        <v>0</v>
+      </c>
+      <c r="CL7" s="45">
+        <f t="shared" ref="CL7" si="41">CK7+CL4</f>
+        <v>0</v>
+      </c>
+      <c r="CM7" s="45">
+        <f t="shared" ref="CM7" si="42">CL7+CM4</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:91" s="38" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="38" t="s">
+    <row r="8" spans="1:91" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="38" t="s">
+      <c r="E8" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="38" t="s">
+      <c r="F8" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="38" t="s">
+      <c r="H8" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="I8" s="38" t="s">
+      <c r="I8" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="38" t="s">
+      <c r="J8" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="K8" s="38" t="s">
+      <c r="K8" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="L8" s="38" t="s">
+      <c r="L8" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="M8" s="38" t="s">
+      <c r="M8" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="N8" s="38" t="s">
+      <c r="N8" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="O8" s="38" t="s">
+      <c r="O8" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="P8" s="38" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="38" t="s">
+      <c r="P8" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="R8" s="38" t="s">
+      <c r="R8" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="S8" s="38" t="s">
+      <c r="S8" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="T8" s="38" t="s">
+      <c r="T8" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="U8" s="38" t="s">
+      <c r="U8" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="V8" s="38" t="s">
+      <c r="V8" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="W8" s="38" t="s">
+      <c r="W8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="X8" s="38" t="s">
+      <c r="X8" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="Y8" s="38" t="s">
+      <c r="Y8" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="Z8" s="38" t="s">
+      <c r="Z8" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="AA8" s="38" t="s">
+      <c r="AA8" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="AB8" s="38" t="s">
+      <c r="AB8" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="AC8" s="38" t="s">
+      <c r="AC8" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="AD8" s="38" t="s">
+      <c r="AD8" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="AE8" s="38" t="s">
+      <c r="AE8" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="AF8" s="38" t="s">
+      <c r="AF8" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="AG8" s="38" t="s">
+      <c r="AG8" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="AH8" s="38" t="s">
+      <c r="AH8" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="AI8" s="38" t="s">
+      <c r="AI8" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="AJ8" s="38" t="s">
+      <c r="AJ8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="AK8" s="38" t="s">
+      <c r="AK8" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="AL8" s="38" t="s">
+      <c r="AL8" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="AM8" s="38" t="s">
+      <c r="AM8" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="AN8" s="38" t="s">
+      <c r="AN8" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="AO8" s="38" t="s">
+      <c r="AO8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="AP8" s="38" t="s">
+      <c r="AP8" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="AQ8" s="38" t="s">
+      <c r="AQ8" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="AR8" s="38" t="s">
+      <c r="AR8" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="AS8" s="38" t="s">
+      <c r="AS8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="AT8" s="38" t="s">
+      <c r="AT8" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="AU8" s="38" t="s">
+      <c r="AU8" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AV8" s="38" t="s">
+      <c r="AV8" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="AW8" s="38" t="s">
+      <c r="AW8" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="AX8" s="38" t="s">
+      <c r="AX8" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="AY8" s="38" t="s">
+      <c r="AY8" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="AZ8" s="38" t="s">
+      <c r="AZ8" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="BA8" s="38" t="s">
+      <c r="BA8" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="BB8" s="38" t="s">
+      <c r="BB8" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="BC8" s="38" t="s">
+      <c r="BC8" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="BD8" s="38" t="s">
+      <c r="BD8" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="BE8" s="38" t="s">
+      <c r="BE8" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="BF8" s="38" t="s">
+      <c r="BF8" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="BG8" s="38" t="s">
+      <c r="BG8" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="BH8" s="38" t="s">
+      <c r="BH8" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="BI8" s="38" t="s">
+      <c r="BI8" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="BJ8" s="38" t="s">
+      <c r="BJ8" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="BK8" s="38" t="s">
+      <c r="BK8" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="BL8" s="38" t="s">
+      <c r="BL8" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="BM8" s="38" t="s">
+      <c r="BM8" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="BN8" s="38" t="s">
+      <c r="BN8" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="BO8" s="38" t="s">
+      <c r="BO8" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="BP8" s="38" t="s">
+      <c r="BP8" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="BQ8" s="38" t="s">
+      <c r="BQ8" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="BR8" s="38" t="s">
+      <c r="BR8" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="BS8" s="38" t="s">
+      <c r="BS8" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="BT8" s="38" t="s">
+      <c r="BT8" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="BU8" s="38" t="s">
+      <c r="BU8" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="BV8" s="38" t="s">
+      <c r="BV8" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="BW8" s="38" t="s">
+      <c r="BW8" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="BX8" s="38" t="s">
+      <c r="BX8" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="BY8" s="38" t="s">
+      <c r="BY8" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="BZ8" s="38" t="s">
+      <c r="BZ8" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="CA8" s="38" t="s">
+      <c r="CA8" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="CB8" s="38" t="s">
+      <c r="CB8" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="CC8" s="38" t="s">
+      <c r="CC8" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="CD8" s="38" t="s">
+      <c r="CD8" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="CE8" s="38" t="s">
+      <c r="CE8" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="CF8" s="38" t="s">
+      <c r="CF8" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="CG8" s="38" t="s">
+      <c r="CG8" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="CH8" s="38" t="s">
+      <c r="CH8" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="CI8" s="38" t="s">
+      <c r="CI8" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="CJ8" s="38" t="s">
+      <c r="CJ8" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="CK8" s="38" t="s">
+      <c r="CK8" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="CL8" s="38" t="s">
+      <c r="CL8" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="CM8" s="38" t="s">
+      <c r="CM8" s="12" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:91" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="39" t="s">
+    <row r="9" spans="1:91" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="40">
+      <c r="B9" s="14">
         <f>SUBTOTAL(103, Table1[[#This Row],[Type]])</f>
         <v>1</v>
       </c>
-      <c r="C9" s="39"/>
-      <c r="D9" s="41">
+      <c r="C9" s="13"/>
+      <c r="D9" s="15">
         <f>SUM(Table1[[#This Row],[w1]:[w87]])</f>
         <v>0</v>
       </c>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="41"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
-      <c r="N9" s="41"/>
-      <c r="O9" s="41"/>
-      <c r="P9" s="41"/>
-      <c r="Q9" s="41"/>
-      <c r="R9" s="41"/>
-      <c r="S9" s="41"/>
-      <c r="T9" s="41"/>
-      <c r="U9" s="41"/>
-      <c r="V9" s="41"/>
-      <c r="W9" s="41"/>
-      <c r="X9" s="41"/>
-      <c r="Y9" s="41"/>
-      <c r="Z9" s="41"/>
-      <c r="AA9" s="41"/>
-      <c r="AB9" s="41"/>
-      <c r="AC9" s="41"/>
-      <c r="AD9" s="41"/>
-      <c r="AE9" s="41"/>
-      <c r="AF9" s="41"/>
-      <c r="AG9" s="41"/>
-      <c r="AH9" s="41"/>
-      <c r="AI9" s="41"/>
-      <c r="AJ9" s="41"/>
-      <c r="AK9" s="41"/>
-      <c r="AL9" s="41"/>
-      <c r="AM9" s="41"/>
-      <c r="AN9" s="41"/>
-      <c r="AO9" s="41"/>
-      <c r="AP9" s="41"/>
-      <c r="AQ9" s="41"/>
-      <c r="AR9" s="41"/>
-      <c r="AS9" s="41"/>
-      <c r="AT9" s="41"/>
-      <c r="AU9" s="41"/>
-      <c r="AV9" s="41"/>
-      <c r="AW9" s="41"/>
-      <c r="AX9" s="41"/>
-      <c r="AY9" s="41"/>
-      <c r="AZ9" s="41"/>
-      <c r="BA9" s="41"/>
-      <c r="BB9" s="41"/>
-      <c r="BC9" s="41"/>
-      <c r="BD9" s="41"/>
-      <c r="BE9" s="41"/>
-      <c r="BF9" s="41"/>
-      <c r="BG9" s="41"/>
-      <c r="BH9" s="41"/>
-      <c r="BI9" s="41"/>
-      <c r="BJ9" s="41"/>
-      <c r="BK9" s="41"/>
-      <c r="BL9" s="41"/>
-      <c r="BM9" s="41"/>
-      <c r="BN9" s="41"/>
-      <c r="BO9" s="41"/>
-      <c r="BP9" s="41"/>
-      <c r="BQ9" s="41"/>
-      <c r="BR9" s="41"/>
-      <c r="BS9" s="41"/>
-      <c r="BT9" s="41"/>
-      <c r="BU9" s="41"/>
-      <c r="BV9" s="41"/>
-      <c r="BW9" s="41"/>
-      <c r="BX9" s="41"/>
-      <c r="BY9" s="41"/>
-      <c r="BZ9" s="41"/>
-      <c r="CA9" s="41"/>
-      <c r="CB9" s="41"/>
-      <c r="CC9" s="41"/>
-      <c r="CD9" s="41"/>
-      <c r="CE9" s="41"/>
-      <c r="CF9" s="41"/>
-      <c r="CG9" s="41"/>
-      <c r="CH9" s="41"/>
-      <c r="CI9" s="41"/>
-      <c r="CJ9" s="41"/>
-      <c r="CK9" s="41"/>
-      <c r="CL9" s="41"/>
-      <c r="CM9" s="41"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="15"/>
+      <c r="R9" s="15"/>
+      <c r="S9" s="15"/>
+      <c r="T9" s="15"/>
+      <c r="U9" s="15"/>
+      <c r="V9" s="15"/>
+      <c r="W9" s="15"/>
+      <c r="X9" s="15"/>
+      <c r="Y9" s="15"/>
+      <c r="Z9" s="15"/>
+      <c r="AA9" s="15"/>
+      <c r="AB9" s="15"/>
+      <c r="AC9" s="15"/>
+      <c r="AD9" s="15"/>
+      <c r="AE9" s="15"/>
+      <c r="AF9" s="15"/>
+      <c r="AG9" s="15"/>
+      <c r="AH9" s="15"/>
+      <c r="AI9" s="15"/>
+      <c r="AJ9" s="15"/>
+      <c r="AK9" s="15"/>
+      <c r="AL9" s="15"/>
+      <c r="AM9" s="15"/>
+      <c r="AN9" s="15"/>
+      <c r="AO9" s="15"/>
+      <c r="AP9" s="15"/>
+      <c r="AQ9" s="15"/>
+      <c r="AR9" s="15"/>
+      <c r="AS9" s="15"/>
+      <c r="AT9" s="15"/>
+      <c r="AU9" s="15"/>
+      <c r="AV9" s="15"/>
+      <c r="AW9" s="15"/>
+      <c r="AX9" s="15"/>
+      <c r="AY9" s="15"/>
+      <c r="AZ9" s="15"/>
+      <c r="BA9" s="15"/>
+      <c r="BB9" s="15"/>
+      <c r="BC9" s="15"/>
+      <c r="BD9" s="15"/>
+      <c r="BE9" s="15"/>
+      <c r="BF9" s="15"/>
+      <c r="BG9" s="15"/>
+      <c r="BH9" s="15"/>
+      <c r="BI9" s="15"/>
+      <c r="BJ9" s="15"/>
+      <c r="BK9" s="15"/>
+      <c r="BL9" s="15"/>
+      <c r="BM9" s="15"/>
+      <c r="BN9" s="15"/>
+      <c r="BO9" s="15"/>
+      <c r="BP9" s="15"/>
+      <c r="BQ9" s="15"/>
+      <c r="BR9" s="15"/>
+      <c r="BS9" s="15"/>
+      <c r="BT9" s="15"/>
+      <c r="BU9" s="15"/>
+      <c r="BV9" s="15"/>
+      <c r="BW9" s="15"/>
+      <c r="BX9" s="15"/>
+      <c r="BY9" s="15"/>
+      <c r="BZ9" s="15"/>
+      <c r="CA9" s="15"/>
+      <c r="CB9" s="15"/>
+      <c r="CC9" s="15"/>
+      <c r="CD9" s="15"/>
+      <c r="CE9" s="15"/>
+      <c r="CF9" s="15"/>
+      <c r="CG9" s="15"/>
+      <c r="CH9" s="15"/>
+      <c r="CI9" s="15"/>
+      <c r="CJ9" s="15"/>
+      <c r="CK9" s="15"/>
+      <c r="CL9" s="15"/>
+      <c r="CM9" s="15"/>
     </row>
     <row r="10" spans="1:91" x14ac:dyDescent="0.25">
-      <c r="A10" s="39" t="s">
+      <c r="A10" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="39">
+      <c r="B10" s="13">
         <f>SUBTOTAL(103, Table1[[#This Row],[Type]])</f>
         <v>1</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="43">
+      <c r="C10" s="13"/>
+      <c r="D10" s="17">
         <f>SUM(Table1[[#This Row],[w1]:[w87]])</f>
         <v>0</v>
       </c>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="41"/>
-      <c r="N10" s="41"/>
-      <c r="O10" s="41"/>
-      <c r="P10" s="41"/>
-      <c r="Q10" s="41"/>
-      <c r="R10" s="41"/>
-      <c r="S10" s="41"/>
-      <c r="T10" s="41"/>
-      <c r="U10" s="41"/>
-      <c r="V10" s="41"/>
-      <c r="W10" s="41"/>
-      <c r="X10" s="41"/>
-      <c r="Y10" s="41"/>
-      <c r="Z10" s="41"/>
-      <c r="AA10" s="41"/>
-      <c r="AB10" s="41"/>
-      <c r="AC10" s="41"/>
-      <c r="AD10" s="41"/>
-      <c r="AE10" s="41"/>
-      <c r="AF10" s="41"/>
-      <c r="AG10" s="41"/>
-      <c r="AH10" s="41"/>
-      <c r="AI10" s="41"/>
-      <c r="AJ10" s="41"/>
-      <c r="AK10" s="41"/>
-      <c r="AL10" s="41"/>
-      <c r="AM10" s="41"/>
-      <c r="AN10" s="41"/>
-      <c r="AO10" s="41"/>
-      <c r="AP10" s="41"/>
-      <c r="AQ10" s="41"/>
-      <c r="AR10" s="41"/>
-      <c r="AS10" s="41"/>
-      <c r="AT10" s="41"/>
-      <c r="AU10" s="41"/>
-      <c r="AV10" s="41"/>
-      <c r="AW10" s="41"/>
-      <c r="AX10" s="41"/>
-      <c r="AY10" s="41"/>
-      <c r="AZ10" s="41"/>
-      <c r="BA10" s="41"/>
-      <c r="BB10" s="41"/>
-      <c r="BC10" s="41"/>
-      <c r="BD10" s="41"/>
-      <c r="BE10" s="41"/>
-      <c r="BF10" s="41"/>
-      <c r="BG10" s="41"/>
-      <c r="BH10" s="41"/>
-      <c r="BI10" s="41"/>
-      <c r="BJ10" s="41"/>
-      <c r="BK10" s="41"/>
-      <c r="BL10" s="41"/>
-      <c r="BM10" s="41"/>
-      <c r="BN10" s="41"/>
-      <c r="BO10" s="41"/>
-      <c r="BP10" s="41"/>
-      <c r="BQ10" s="41"/>
-      <c r="BR10" s="41"/>
-      <c r="BS10" s="41"/>
-      <c r="BT10" s="41"/>
-      <c r="BU10" s="41"/>
-      <c r="BV10" s="41"/>
-      <c r="BW10" s="41"/>
-      <c r="BX10" s="41"/>
-      <c r="BY10" s="41"/>
-      <c r="BZ10" s="41"/>
-      <c r="CA10" s="41"/>
-      <c r="CB10" s="41"/>
-      <c r="CC10" s="41"/>
-      <c r="CD10" s="41"/>
-      <c r="CE10" s="41"/>
-      <c r="CF10" s="41"/>
-      <c r="CG10" s="41"/>
-      <c r="CH10" s="41"/>
-      <c r="CI10" s="41"/>
-      <c r="CJ10" s="41"/>
-      <c r="CK10" s="41"/>
-      <c r="CL10" s="41"/>
-      <c r="CM10" s="41"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="15"/>
+      <c r="R10" s="15"/>
+      <c r="S10" s="15"/>
+      <c r="T10" s="15"/>
+      <c r="U10" s="15"/>
+      <c r="V10" s="15"/>
+      <c r="W10" s="15"/>
+      <c r="X10" s="15"/>
+      <c r="Y10" s="15"/>
+      <c r="Z10" s="15"/>
+      <c r="AA10" s="15"/>
+      <c r="AB10" s="15"/>
+      <c r="AC10" s="15"/>
+      <c r="AD10" s="15"/>
+      <c r="AE10" s="15"/>
+      <c r="AF10" s="15"/>
+      <c r="AG10" s="15"/>
+      <c r="AH10" s="15"/>
+      <c r="AI10" s="15"/>
+      <c r="AJ10" s="15"/>
+      <c r="AK10" s="15"/>
+      <c r="AL10" s="15"/>
+      <c r="AM10" s="15"/>
+      <c r="AN10" s="15"/>
+      <c r="AO10" s="15"/>
+      <c r="AP10" s="15"/>
+      <c r="AQ10" s="15"/>
+      <c r="AR10" s="15"/>
+      <c r="AS10" s="15"/>
+      <c r="AT10" s="15"/>
+      <c r="AU10" s="15"/>
+      <c r="AV10" s="15"/>
+      <c r="AW10" s="15"/>
+      <c r="AX10" s="15"/>
+      <c r="AY10" s="15"/>
+      <c r="AZ10" s="15"/>
+      <c r="BA10" s="15"/>
+      <c r="BB10" s="15"/>
+      <c r="BC10" s="15"/>
+      <c r="BD10" s="15"/>
+      <c r="BE10" s="15"/>
+      <c r="BF10" s="15"/>
+      <c r="BG10" s="15"/>
+      <c r="BH10" s="15"/>
+      <c r="BI10" s="15"/>
+      <c r="BJ10" s="15"/>
+      <c r="BK10" s="15"/>
+      <c r="BL10" s="15"/>
+      <c r="BM10" s="15"/>
+      <c r="BN10" s="15"/>
+      <c r="BO10" s="15"/>
+      <c r="BP10" s="15"/>
+      <c r="BQ10" s="15"/>
+      <c r="BR10" s="15"/>
+      <c r="BS10" s="15"/>
+      <c r="BT10" s="15"/>
+      <c r="BU10" s="15"/>
+      <c r="BV10" s="15"/>
+      <c r="BW10" s="15"/>
+      <c r="BX10" s="15"/>
+      <c r="BY10" s="15"/>
+      <c r="BZ10" s="15"/>
+      <c r="CA10" s="15"/>
+      <c r="CB10" s="15"/>
+      <c r="CC10" s="15"/>
+      <c r="CD10" s="15"/>
+      <c r="CE10" s="15"/>
+      <c r="CF10" s="15"/>
+      <c r="CG10" s="15"/>
+      <c r="CH10" s="15"/>
+      <c r="CI10" s="15"/>
+      <c r="CJ10" s="15"/>
+      <c r="CK10" s="15"/>
+      <c r="CL10" s="15"/>
+      <c r="CM10" s="15"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="43">
-    <mergeCell ref="W1:BV1"/>
-    <mergeCell ref="BW1:CM1"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="N2:Q2"/>
-    <mergeCell ref="AA2:AD2"/>
-    <mergeCell ref="AN2:AQ2"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="AA3:AD3"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="R3:V3"/>
+    <mergeCell ref="AJ3:AM3"/>
+    <mergeCell ref="BF2:BI2"/>
+    <mergeCell ref="BJ2:BM2"/>
+    <mergeCell ref="BN2:BR2"/>
+    <mergeCell ref="BS3:BV3"/>
+    <mergeCell ref="BW3:BZ3"/>
+    <mergeCell ref="CF3:CI3"/>
+    <mergeCell ref="CJ3:CM3"/>
+    <mergeCell ref="CA3:CE3"/>
     <mergeCell ref="BF3:BI3"/>
     <mergeCell ref="BJ3:BM3"/>
     <mergeCell ref="BN3:BR3"/>
@@ -7746,25 +6942,28 @@
     <mergeCell ref="AR2:AV2"/>
     <mergeCell ref="AR3:AV3"/>
     <mergeCell ref="AN3:AQ3"/>
+    <mergeCell ref="AJ2:AM2"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="AA3:AD3"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="R3:V3"/>
+    <mergeCell ref="W1:BV1"/>
+    <mergeCell ref="BW1:CM1"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="N2:Q2"/>
+    <mergeCell ref="AA2:AD2"/>
+    <mergeCell ref="AN2:AQ2"/>
     <mergeCell ref="E1:V1"/>
-    <mergeCell ref="BS3:BV3"/>
-    <mergeCell ref="BW3:BZ3"/>
-    <mergeCell ref="CF3:CI3"/>
-    <mergeCell ref="CJ3:CM3"/>
-    <mergeCell ref="CA3:CE3"/>
     <mergeCell ref="BS2:BV2"/>
     <mergeCell ref="BW2:BZ2"/>
     <mergeCell ref="CA2:CE2"/>
     <mergeCell ref="CF2:CI2"/>
     <mergeCell ref="CJ2:CM2"/>
-    <mergeCell ref="AJ2:AM2"/>
-    <mergeCell ref="AJ3:AM3"/>
-    <mergeCell ref="BF2:BI2"/>
-    <mergeCell ref="BJ2:BM2"/>
-    <mergeCell ref="BN2:BR2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" error="از لیست کشویی یک مقدار را انتخاب کنید" sqref="A9:A10" xr:uid="{3574D37E-C1E9-49D7-A49D-23277B81A7FD}">
       <formula1>List</formula1>
     </dataValidation>
